--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -972,7 +973,6 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -981,8 +981,6 @@
       <c r="G2" t="n">
         <v>2630</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1006,7 +1004,6 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1015,8 +1012,6 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1040,7 +1035,6 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1049,8 +1043,6 @@
       <c r="G4" t="n">
         <v>274</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1074,7 +1066,6 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1083,8 +1074,6 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1108,7 +1097,6 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1117,8 +1105,6 @@
       <c r="G6" t="n">
         <v>229.332</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1142,7 +1128,6 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1151,8 +1136,6 @@
       <c r="G7" t="n">
         <v>2630</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1176,7 +1159,6 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1185,8 +1167,6 @@
       <c r="G8" t="n">
         <v>800</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1210,7 +1190,6 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1219,8 +1198,6 @@
       <c r="G9" t="n">
         <v>274</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1244,7 +1221,6 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1253,8 +1229,6 @@
       <c r="G10" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1278,7 +1252,6 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1287,8 +1260,6 @@
       <c r="G11" t="n">
         <v>229.332</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1312,7 +1283,6 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1321,8 +1291,6 @@
       <c r="G12" t="n">
         <v>2630</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1346,7 +1314,6 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1355,8 +1322,6 @@
       <c r="G13" t="n">
         <v>800</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1380,7 +1345,6 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1389,8 +1353,6 @@
       <c r="G14" t="n">
         <v>274</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1414,7 +1376,6 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1423,8 +1384,6 @@
       <c r="G15" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1448,7 +1407,6 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1457,8 +1415,6 @@
       <c r="G16" t="n">
         <v>229.332</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1482,7 +1438,6 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1491,8 +1446,6 @@
       <c r="G17" t="n">
         <v>7.004</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1516,7 +1469,6 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1525,8 +1477,6 @@
       <c r="G18" t="n">
         <v>103</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1550,7 +1500,6 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1559,8 +1508,6 @@
       <c r="G19" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1584,7 +1531,6 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1593,8 +1539,6 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1618,7 +1562,6 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1627,8 +1570,6 @@
       <c r="G21" t="n">
         <v>20</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1652,7 +1593,6 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1661,8 +1601,6 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1686,7 +1624,6 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1695,8 +1632,6 @@
       <c r="G23" t="n">
         <v>60</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1720,7 +1655,6 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1729,8 +1663,6 @@
       <c r="G24" t="n">
         <v>2630</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1754,7 +1686,6 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1763,8 +1694,6 @@
       <c r="G25" t="n">
         <v>800</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1788,7 +1717,6 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1797,8 +1725,6 @@
       <c r="G26" t="n">
         <v>274</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1822,7 +1748,6 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1831,8 +1756,6 @@
       <c r="G27" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1856,7 +1779,6 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1865,8 +1787,6 @@
       <c r="G28" t="n">
         <v>229.332</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1890,7 +1810,6 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1899,8 +1818,6 @@
       <c r="G29" t="n">
         <v>7.004</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1924,7 +1841,6 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1933,8 +1849,6 @@
       <c r="G30" t="n">
         <v>103</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1958,7 +1872,6 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1967,8 +1880,6 @@
       <c r="G31" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1992,7 +1903,6 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2001,8 +1911,6 @@
       <c r="G32" t="n">
         <v>20</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2026,7 +1934,6 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2035,8 +1942,6 @@
       <c r="G33" t="n">
         <v>20</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2060,7 +1965,6 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2069,8 +1973,6 @@
       <c r="G34" t="n">
         <v>20</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2094,7 +1996,6 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2103,8 +2004,6 @@
       <c r="G35" t="n">
         <v>60</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2128,7 +2027,6 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2137,8 +2035,6 @@
       <c r="G36" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2162,7 +2058,6 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2171,8 +2066,6 @@
       <c r="G37" t="n">
         <v>61.8</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2196,7 +2089,6 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2205,8 +2097,6 @@
       <c r="G38" t="n">
         <v>54.384</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2230,7 +2120,6 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2239,8 +2128,6 @@
       <c r="G39" t="n">
         <v>2630</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2264,7 +2151,6 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2273,8 +2159,6 @@
       <c r="G40" t="n">
         <v>800</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2298,7 +2182,6 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2307,8 +2190,6 @@
       <c r="G41" t="n">
         <v>274</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2332,7 +2213,6 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2341,8 +2221,6 @@
       <c r="G42" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2366,7 +2244,6 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2375,8 +2252,6 @@
       <c r="G43" t="n">
         <v>229.332</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2400,7 +2275,6 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2409,8 +2283,6 @@
       <c r="G44" t="n">
         <v>7.004</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2434,7 +2306,6 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2443,8 +2314,6 @@
       <c r="G45" t="n">
         <v>103</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2468,7 +2337,6 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2477,8 +2345,6 @@
       <c r="G46" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2502,7 +2368,6 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2511,8 +2376,6 @@
       <c r="G47" t="n">
         <v>20</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2536,7 +2399,6 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2545,8 +2407,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2570,7 +2430,6 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2579,8 +2438,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2604,7 +2461,6 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2613,8 +2469,6 @@
       <c r="G50" t="n">
         <v>60</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2638,7 +2492,6 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2647,8 +2500,6 @@
       <c r="G51" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2672,7 +2523,6 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2681,8 +2531,6 @@
       <c r="G52" t="n">
         <v>61.8</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2706,7 +2554,6 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2715,8 +2562,6 @@
       <c r="G53" t="n">
         <v>54.384</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2740,7 +2585,6 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2749,8 +2593,6 @@
       <c r="G54" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2774,7 +2616,6 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2783,8 +2624,6 @@
       <c r="G55" t="n">
         <v>1613.23</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2808,7 +2647,6 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2817,8 +2655,6 @@
       <c r="G56" t="n">
         <v>645.48</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2842,7 +2678,6 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2851,8 +2686,6 @@
       <c r="G57" t="n">
         <v>500.5</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2876,7 +2709,6 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2885,8 +2717,6 @@
       <c r="G58" t="n">
         <v>283.5</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2910,7 +2740,6 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2919,8 +2748,6 @@
       <c r="G59" t="n">
         <v>250</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2944,7 +2771,6 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2953,8 +2779,6 @@
       <c r="G60" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2978,7 +2802,6 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2987,8 +2810,6 @@
       <c r="G61" t="n">
         <v>105.34</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3012,7 +2833,6 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -3021,8 +2841,6 @@
       <c r="G62" t="n">
         <v>96.899</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3046,7 +2864,6 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -3055,8 +2872,6 @@
       <c r="G63" t="n">
         <v>38.7596</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3080,7 +2895,6 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -3089,8 +2903,6 @@
       <c r="G64" t="n">
         <v>103</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3114,7 +2926,6 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -3123,8 +2934,6 @@
       <c r="G65" t="n">
         <v>51.5</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3148,7 +2957,6 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -3157,8 +2965,6 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3182,7 +2988,6 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -3191,8 +2996,6 @@
       <c r="G67" t="n">
         <v>61.8</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3216,7 +3019,6 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3225,8 +3027,6 @@
       <c r="G68" t="n">
         <v>54.384</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3250,7 +3050,6 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3259,8 +3058,6 @@
       <c r="G69" t="n">
         <v>50</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3284,7 +3081,6 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3293,8 +3089,6 @@
       <c r="G70" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3318,7 +3112,6 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3327,8 +3120,6 @@
       <c r="G71" t="n">
         <v>50</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3352,7 +3143,6 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3361,8 +3151,6 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3386,7 +3174,6 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3395,8 +3182,6 @@
       <c r="G73" t="n">
         <v>7.004</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3420,7 +3205,6 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3429,8 +3213,6 @@
       <c r="G74" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3454,7 +3236,6 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3463,8 +3244,6 @@
       <c r="G75" t="n">
         <v>27.4667</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3488,7 +3267,6 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3497,8 +3275,6 @@
       <c r="G76" t="n">
         <v>36.9083</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3522,7 +3298,6 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3531,8 +3306,6 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3556,7 +3329,6 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3565,8 +3337,6 @@
       <c r="G78" t="n">
         <v>60</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3590,7 +3360,6 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3599,8 +3368,6 @@
       <c r="G79" t="n">
         <v>20</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3624,7 +3391,6 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3633,8 +3399,6 @@
       <c r="G80" t="n">
         <v>60</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3658,7 +3422,6 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3667,8 +3430,6 @@
       <c r="G81" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3692,7 +3453,6 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3701,8 +3461,6 @@
       <c r="G82" t="n">
         <v>20</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3726,7 +3484,6 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3735,8 +3492,6 @@
       <c r="G83" t="n">
         <v>20</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3760,7 +3515,6 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3769,8 +3523,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3794,7 +3546,6 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3803,8 +3554,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3828,7 +3577,6 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3837,8 +3585,6 @@
       <c r="G86" t="n">
         <v>20</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3862,7 +3608,6 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3871,8 +3616,6 @@
       <c r="G87" t="n">
         <v>20</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3896,7 +3639,6 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3905,11 +3647,3099 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴流量15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>股权存量87条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>字段类型+t0存在检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-933.7074</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-669.3701</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="E6" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5198.0447</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4635</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-563.0447</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4635</v>
+      </c>
+      <c r="E7" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5568.7074</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-820.6586</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="E8" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5681.7562</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4880.2539</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-801.5023</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>丰利财富</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-66.66800000000001</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>274</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274</v>
+      </c>
+      <c r="G10" t="n">
+        <v>274</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>800</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>825</v>
+      </c>
+      <c r="G11" t="n">
+        <v>800</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G12" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>274</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>274</v>
+      </c>
+      <c r="G15" t="n">
+        <v>274</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>800</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>825</v>
+      </c>
+      <c r="G16" t="n">
+        <v>800</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G17" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>103</v>
+      </c>
+      <c r="F18" t="n">
+        <v>103</v>
+      </c>
+      <c r="G18" t="n">
+        <v>103</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F25" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="G25" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F28" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="G28" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>274</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>274</v>
+      </c>
+      <c r="G29" t="n">
+        <v>274</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>800</v>
+      </c>
+      <c r="E30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" t="n">
+        <v>825</v>
+      </c>
+      <c r="G30" t="n">
+        <v>800</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G31" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>103</v>
+      </c>
+      <c r="E32" t="n">
+        <v>103</v>
+      </c>
+      <c r="F32" t="n">
+        <v>206</v>
+      </c>
+      <c r="G32" t="n">
+        <v>103</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" t="n">
+        <v>120</v>
+      </c>
+      <c r="G33" t="n">
+        <v>60</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F34" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="G34" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F35" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="n">
+        <v>40</v>
+      </c>
+      <c r="G39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="E40" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F40" t="n">
+        <v>68.6666</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-34.3333</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="n">
+        <v>40</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="E43" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F43" t="n">
+        <v>108.768</v>
+      </c>
+      <c r="G43" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-54.384</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>274</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>274</v>
+      </c>
+      <c r="G44" t="n">
+        <v>274</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>800</v>
+      </c>
+      <c r="E45" t="n">
+        <v>25</v>
+      </c>
+      <c r="F45" t="n">
+        <v>825</v>
+      </c>
+      <c r="G45" t="n">
+        <v>800</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G46" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>103</v>
+      </c>
+      <c r="E47" t="n">
+        <v>103</v>
+      </c>
+      <c r="F47" t="n">
+        <v>206</v>
+      </c>
+      <c r="G47" t="n">
+        <v>103</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>60</v>
+      </c>
+      <c r="E48" t="n">
+        <v>60</v>
+      </c>
+      <c r="F48" t="n">
+        <v>120</v>
+      </c>
+      <c r="G48" t="n">
+        <v>60</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="E49" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F49" t="n">
+        <v>508.9574</v>
+      </c>
+      <c r="G49" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-254.4787</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F50" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G50" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G51" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>20</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" t="n">
+        <v>40</v>
+      </c>
+      <c r="G53" t="n">
+        <v>20</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" t="n">
+        <v>40</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>火炬电子</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="F55" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="G55" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="E56" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F56" t="n">
+        <v>68.6666</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-34.3333</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>20</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20</v>
+      </c>
+      <c r="F57" t="n">
+        <v>40</v>
+      </c>
+      <c r="G57" t="n">
+        <v>20</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>274</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>274</v>
+      </c>
+      <c r="G58" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-168.66</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>余满芬</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>20</v>
+      </c>
+      <c r="H59" t="n">
+        <v>20</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>800</v>
+      </c>
+      <c r="E60" t="n">
+        <v>25</v>
+      </c>
+      <c r="F60" t="n">
+        <v>825</v>
+      </c>
+      <c r="G60" t="n">
+        <v>645.48</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-179.52</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>103</v>
+      </c>
+      <c r="E61" t="n">
+        <v>103</v>
+      </c>
+      <c r="F61" t="n">
+        <v>206</v>
+      </c>
+      <c r="G61" t="n">
+        <v>103</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>厦门西堤</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="F62" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="G62" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>60</v>
+      </c>
+      <c r="E63" t="n">
+        <v>60</v>
+      </c>
+      <c r="F63" t="n">
+        <v>120</v>
+      </c>
+      <c r="G63" t="n">
+        <v>60</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="E64" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F64" t="n">
+        <v>508.9574</v>
+      </c>
+      <c r="G64" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-254.4787</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E65" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F65" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G65" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G66" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>不变</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>富海深湾</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" t="n">
+        <v>50</v>
+      </c>
+      <c r="H67" t="n">
+        <v>50</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>富海节能</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H68" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1613.23</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-1016.77</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>20</v>
+      </c>
+      <c r="E70" t="n">
+        <v>20</v>
+      </c>
+      <c r="F70" t="n">
+        <v>40</v>
+      </c>
+      <c r="G70" t="n">
+        <v>60</v>
+      </c>
+      <c r="H70" t="n">
+        <v>20</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>沈笑彦</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>20</v>
+      </c>
+      <c r="H71" t="n">
+        <v>20</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>湘裕君源</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="n">
+        <v>15.9535</v>
+      </c>
+      <c r="H72" t="n">
+        <v>15.9535</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>福建开京</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>20</v>
+      </c>
+      <c r="H73" t="n">
+        <v>20</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>芜湖富海</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>郦韩英</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="n">
+        <v>20</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>镇江红土</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>50</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>鸿迪投资</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>36.9083</v>
+      </c>
+      <c r="H77" t="n">
+        <v>36.9083</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,6 +972,7 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -981,6 +981,8 @@
       <c r="G2" t="n">
         <v>2630</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1004,6 +1006,7 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1012,6 +1015,8 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1035,6 +1040,7 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1043,6 +1049,8 @@
       <c r="G4" t="n">
         <v>274</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1066,6 +1074,7 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1074,6 +1083,8 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1097,6 +1108,7 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1105,6 +1117,8 @@
       <c r="G6" t="n">
         <v>229.332</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1128,6 +1142,7 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1136,6 +1151,8 @@
       <c r="G7" t="n">
         <v>2630</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1159,6 +1176,7 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1167,6 +1185,8 @@
       <c r="G8" t="n">
         <v>800</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1190,6 +1210,7 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1198,6 +1219,8 @@
       <c r="G9" t="n">
         <v>274</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1221,6 +1244,7 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1229,6 +1253,8 @@
       <c r="G10" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1252,6 +1278,7 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1260,6 +1287,8 @@
       <c r="G11" t="n">
         <v>229.332</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1283,6 +1312,7 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1291,6 +1321,8 @@
       <c r="G12" t="n">
         <v>2630</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1314,6 +1346,7 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1322,6 +1355,8 @@
       <c r="G13" t="n">
         <v>800</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1345,6 +1380,7 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1353,6 +1389,8 @@
       <c r="G14" t="n">
         <v>274</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1376,6 +1414,7 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1384,6 +1423,8 @@
       <c r="G15" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1407,6 +1448,7 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1415,6 +1457,8 @@
       <c r="G16" t="n">
         <v>229.332</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1438,6 +1482,7 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1446,6 +1491,8 @@
       <c r="G17" t="n">
         <v>7.004</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1469,6 +1516,7 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1477,6 +1525,8 @@
       <c r="G18" t="n">
         <v>103</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1500,6 +1550,7 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1508,6 +1559,8 @@
       <c r="G19" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1531,6 +1584,7 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1539,6 +1593,8 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1562,6 +1618,7 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1570,6 +1627,8 @@
       <c r="G21" t="n">
         <v>20</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1593,6 +1652,7 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1601,6 +1661,8 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1624,6 +1686,7 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1632,6 +1695,8 @@
       <c r="G23" t="n">
         <v>60</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1655,6 +1720,7 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1663,6 +1729,8 @@
       <c r="G24" t="n">
         <v>2630</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1686,6 +1754,7 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1694,6 +1763,8 @@
       <c r="G25" t="n">
         <v>800</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1717,6 +1788,7 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1725,6 +1797,8 @@
       <c r="G26" t="n">
         <v>274</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1748,6 +1822,7 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1756,6 +1831,8 @@
       <c r="G27" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1779,6 +1856,7 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1787,6 +1865,8 @@
       <c r="G28" t="n">
         <v>229.332</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1810,6 +1890,7 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1818,6 +1899,8 @@
       <c r="G29" t="n">
         <v>7.004</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1841,6 +1924,7 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1849,6 +1933,8 @@
       <c r="G30" t="n">
         <v>103</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1872,6 +1958,7 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1880,6 +1967,8 @@
       <c r="G31" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1903,6 +1992,7 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1911,6 +2001,8 @@
       <c r="G32" t="n">
         <v>20</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1934,6 +2026,7 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1942,6 +2035,8 @@
       <c r="G33" t="n">
         <v>20</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1965,6 +2060,7 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1973,6 +2069,8 @@
       <c r="G34" t="n">
         <v>20</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1996,6 +2094,7 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2004,6 +2103,8 @@
       <c r="G35" t="n">
         <v>60</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2027,6 +2128,7 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2035,6 +2137,8 @@
       <c r="G36" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2058,6 +2162,7 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2066,6 +2171,8 @@
       <c r="G37" t="n">
         <v>61.8</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2089,6 +2196,7 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2097,6 +2205,8 @@
       <c r="G38" t="n">
         <v>54.384</v>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2120,6 +2230,7 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2128,6 +2239,8 @@
       <c r="G39" t="n">
         <v>2630</v>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2151,6 +2264,7 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2159,6 +2273,8 @@
       <c r="G40" t="n">
         <v>800</v>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2182,6 +2298,7 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2190,6 +2307,8 @@
       <c r="G41" t="n">
         <v>274</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2213,6 +2332,7 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2221,6 +2341,8 @@
       <c r="G42" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2244,6 +2366,7 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2252,6 +2375,8 @@
       <c r="G43" t="n">
         <v>229.332</v>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2275,6 +2400,7 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2283,6 +2409,8 @@
       <c r="G44" t="n">
         <v>7.004</v>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2306,6 +2434,7 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2314,6 +2443,8 @@
       <c r="G45" t="n">
         <v>103</v>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2337,6 +2468,7 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2345,6 +2477,8 @@
       <c r="G46" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2368,6 +2502,7 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2376,6 +2511,8 @@
       <c r="G47" t="n">
         <v>20</v>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2399,6 +2536,7 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2407,6 +2545,8 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2430,6 +2570,7 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2438,6 +2579,8 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2461,6 +2604,7 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2469,6 +2613,8 @@
       <c r="G50" t="n">
         <v>60</v>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2492,6 +2638,7 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2500,6 +2647,8 @@
       <c r="G51" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2523,6 +2672,7 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2531,6 +2681,8 @@
       <c r="G52" t="n">
         <v>61.8</v>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2554,6 +2706,7 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2562,6 +2715,8 @@
       <c r="G53" t="n">
         <v>54.384</v>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2585,6 +2740,7 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2593,6 +2749,8 @@
       <c r="G54" t="n">
         <v>113.0488</v>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2616,6 +2774,7 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2624,6 +2783,8 @@
       <c r="G55" t="n">
         <v>1613.23</v>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2647,6 +2808,7 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2655,6 +2817,8 @@
       <c r="G56" t="n">
         <v>645.48</v>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2678,6 +2842,7 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2686,6 +2851,8 @@
       <c r="G57" t="n">
         <v>500.5</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2709,6 +2876,7 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2717,6 +2885,8 @@
       <c r="G58" t="n">
         <v>283.5</v>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2740,6 +2910,7 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2748,6 +2919,8 @@
       <c r="G59" t="n">
         <v>250</v>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2771,6 +2944,7 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2779,6 +2953,8 @@
       <c r="G60" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2802,6 +2978,7 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2810,6 +2987,8 @@
       <c r="G61" t="n">
         <v>105.34</v>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2833,6 +3012,7 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -2841,6 +3021,8 @@
       <c r="G62" t="n">
         <v>96.899</v>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2864,6 +3046,7 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -2872,6 +3055,8 @@
       <c r="G63" t="n">
         <v>38.7596</v>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2895,6 +3080,7 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2903,6 +3089,8 @@
       <c r="G64" t="n">
         <v>103</v>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2926,6 +3114,7 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -2934,6 +3123,8 @@
       <c r="G65" t="n">
         <v>51.5</v>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2957,6 +3148,7 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -2965,6 +3157,8 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2988,6 +3182,7 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2996,6 +3191,8 @@
       <c r="G67" t="n">
         <v>61.8</v>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3019,6 +3216,7 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3027,6 +3225,8 @@
       <c r="G68" t="n">
         <v>54.384</v>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3050,6 +3250,7 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3058,6 +3259,8 @@
       <c r="G69" t="n">
         <v>50</v>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3081,6 +3284,7 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3089,6 +3293,8 @@
       <c r="G70" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3112,6 +3318,7 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3120,6 +3327,8 @@
       <c r="G71" t="n">
         <v>50</v>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3143,6 +3352,7 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3151,6 +3361,8 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3174,6 +3386,7 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3182,6 +3395,8 @@
       <c r="G73" t="n">
         <v>7.004</v>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3205,6 +3420,7 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3213,6 +3429,8 @@
       <c r="G74" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3236,6 +3454,7 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3244,6 +3463,8 @@
       <c r="G75" t="n">
         <v>27.4667</v>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3267,6 +3488,7 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3275,6 +3497,8 @@
       <c r="G76" t="n">
         <v>36.9083</v>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3298,6 +3522,7 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3306,6 +3531,8 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3329,6 +3556,7 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3337,6 +3565,8 @@
       <c r="G78" t="n">
         <v>60</v>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3360,6 +3590,7 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3368,6 +3599,8 @@
       <c r="G79" t="n">
         <v>20</v>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3391,6 +3624,7 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3399,6 +3633,8 @@
       <c r="G80" t="n">
         <v>60</v>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3422,6 +3658,7 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3430,6 +3667,8 @@
       <c r="G81" t="n">
         <v>113.0488</v>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3453,6 +3692,7 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3461,6 +3701,8 @@
       <c r="G82" t="n">
         <v>20</v>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3484,6 +3726,7 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3492,6 +3735,8 @@
       <c r="G83" t="n">
         <v>20</v>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3515,6 +3760,7 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3523,6 +3769,8 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3546,6 +3794,7 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3554,6 +3803,8 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3577,6 +3828,7 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3585,6 +3837,8 @@
       <c r="G86" t="n">
         <v>20</v>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3608,6 +3862,7 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3616,6 +3871,8 @@
       <c r="G87" t="n">
         <v>20</v>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3639,6 +3896,7 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3647,3099 +3905,11 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J77"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量87条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>字段类型+t0存在检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-933.7074</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-669.3701</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="E6" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5198.0447</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4635</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-563.0447</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4635</v>
-      </c>
-      <c r="E7" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5568.7074</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-820.6586</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="E8" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5681.7562</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4880.2539</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-801.5023</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>丰利财富</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-66.66800000000001</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>274</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>274</v>
-      </c>
-      <c r="G10" t="n">
-        <v>274</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>800</v>
-      </c>
-      <c r="E11" t="n">
-        <v>25</v>
-      </c>
-      <c r="F11" t="n">
-        <v>825</v>
-      </c>
-      <c r="G11" t="n">
-        <v>800</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G12" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>274</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>274</v>
-      </c>
-      <c r="G15" t="n">
-        <v>274</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>800</v>
-      </c>
-      <c r="E16" t="n">
-        <v>25</v>
-      </c>
-      <c r="F16" t="n">
-        <v>825</v>
-      </c>
-      <c r="G16" t="n">
-        <v>800</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G17" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>103</v>
-      </c>
-      <c r="F18" t="n">
-        <v>103</v>
-      </c>
-      <c r="G18" t="n">
-        <v>103</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>60</v>
-      </c>
-      <c r="F19" t="n">
-        <v>60</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23" t="n">
-        <v>20</v>
-      </c>
-      <c r="G23" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>20</v>
-      </c>
-      <c r="F24" t="n">
-        <v>20</v>
-      </c>
-      <c r="G24" t="n">
-        <v>20</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F25" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="G25" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" t="n">
-        <v>20</v>
-      </c>
-      <c r="G26" t="n">
-        <v>20</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F27" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="G27" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F28" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="G28" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>274</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>274</v>
-      </c>
-      <c r="G29" t="n">
-        <v>274</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>800</v>
-      </c>
-      <c r="E30" t="n">
-        <v>25</v>
-      </c>
-      <c r="F30" t="n">
-        <v>825</v>
-      </c>
-      <c r="G30" t="n">
-        <v>800</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G31" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>103</v>
-      </c>
-      <c r="E32" t="n">
-        <v>103</v>
-      </c>
-      <c r="F32" t="n">
-        <v>206</v>
-      </c>
-      <c r="G32" t="n">
-        <v>103</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" t="n">
-        <v>120</v>
-      </c>
-      <c r="G33" t="n">
-        <v>60</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F34" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="G34" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E35" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F35" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G35" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G36" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>20</v>
-      </c>
-      <c r="E38" t="n">
-        <v>20</v>
-      </c>
-      <c r="F38" t="n">
-        <v>40</v>
-      </c>
-      <c r="G38" t="n">
-        <v>20</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E39" t="n">
-        <v>20</v>
-      </c>
-      <c r="F39" t="n">
-        <v>40</v>
-      </c>
-      <c r="G39" t="n">
-        <v>20</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="E40" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F40" t="n">
-        <v>68.6666</v>
-      </c>
-      <c r="G40" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-34.3333</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>20</v>
-      </c>
-      <c r="E41" t="n">
-        <v>20</v>
-      </c>
-      <c r="F41" t="n">
-        <v>40</v>
-      </c>
-      <c r="G41" t="n">
-        <v>20</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F42" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="G42" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-61.8</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="E43" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F43" t="n">
-        <v>108.768</v>
-      </c>
-      <c r="G43" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-54.384</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>274</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>274</v>
-      </c>
-      <c r="G44" t="n">
-        <v>274</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>800</v>
-      </c>
-      <c r="E45" t="n">
-        <v>25</v>
-      </c>
-      <c r="F45" t="n">
-        <v>825</v>
-      </c>
-      <c r="G45" t="n">
-        <v>800</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G46" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>103</v>
-      </c>
-      <c r="E47" t="n">
-        <v>103</v>
-      </c>
-      <c r="F47" t="n">
-        <v>206</v>
-      </c>
-      <c r="G47" t="n">
-        <v>103</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>60</v>
-      </c>
-      <c r="E48" t="n">
-        <v>60</v>
-      </c>
-      <c r="F48" t="n">
-        <v>120</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="E49" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F49" t="n">
-        <v>508.9574</v>
-      </c>
-      <c r="G49" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-254.4787</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E50" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F50" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G50" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G51" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>20</v>
-      </c>
-      <c r="E53" t="n">
-        <v>20</v>
-      </c>
-      <c r="F53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G53" t="n">
-        <v>20</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" t="n">
-        <v>20</v>
-      </c>
-      <c r="F54" t="n">
-        <v>40</v>
-      </c>
-      <c r="G54" t="n">
-        <v>20</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>火炬电子</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="F55" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="G55" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="E56" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F56" t="n">
-        <v>68.6666</v>
-      </c>
-      <c r="G56" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-34.3333</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>20</v>
-      </c>
-      <c r="E57" t="n">
-        <v>20</v>
-      </c>
-      <c r="F57" t="n">
-        <v>40</v>
-      </c>
-      <c r="G57" t="n">
-        <v>20</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>274</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>274</v>
-      </c>
-      <c r="G58" t="n">
-        <v>105.34</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-168.66</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>余满芬</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>20</v>
-      </c>
-      <c r="H59" t="n">
-        <v>20</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>800</v>
-      </c>
-      <c r="E60" t="n">
-        <v>25</v>
-      </c>
-      <c r="F60" t="n">
-        <v>825</v>
-      </c>
-      <c r="G60" t="n">
-        <v>645.48</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-179.52</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>103</v>
-      </c>
-      <c r="E61" t="n">
-        <v>103</v>
-      </c>
-      <c r="F61" t="n">
-        <v>206</v>
-      </c>
-      <c r="G61" t="n">
-        <v>103</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>厦门西堤</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="F62" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="G62" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>60</v>
-      </c>
-      <c r="E63" t="n">
-        <v>60</v>
-      </c>
-      <c r="F63" t="n">
-        <v>120</v>
-      </c>
-      <c r="G63" t="n">
-        <v>60</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="E64" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F64" t="n">
-        <v>508.9574</v>
-      </c>
-      <c r="G64" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-254.4787</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E65" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F65" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G65" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G66" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>不变</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>富海深湾</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" t="n">
-        <v>50</v>
-      </c>
-      <c r="H67" t="n">
-        <v>50</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>富海节能</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H68" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G69" t="n">
-        <v>1613.23</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-1016.77</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>20</v>
-      </c>
-      <c r="E70" t="n">
-        <v>20</v>
-      </c>
-      <c r="F70" t="n">
-        <v>40</v>
-      </c>
-      <c r="G70" t="n">
-        <v>60</v>
-      </c>
-      <c r="H70" t="n">
-        <v>20</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>沈笑彦</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>20</v>
-      </c>
-      <c r="H71" t="n">
-        <v>20</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>湘裕君源</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" t="n">
-        <v>15.9535</v>
-      </c>
-      <c r="H72" t="n">
-        <v>15.9535</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>福建开京</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>20</v>
-      </c>
-      <c r="H73" t="n">
-        <v>20</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>芜湖富海</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>283.5</v>
-      </c>
-      <c r="H74" t="n">
-        <v>283.5</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>郦韩英</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>20</v>
-      </c>
-      <c r="H75" t="n">
-        <v>20</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>镇江红土</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>50</v>
-      </c>
-      <c r="H76" t="n">
-        <v>50</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>鸿迪投资</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>36.9083</v>
-      </c>
-      <c r="H77" t="n">
-        <v>36.9083</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -972,7 +973,6 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -981,8 +981,6 @@
       <c r="G2" t="n">
         <v>2630</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1006,7 +1004,6 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1015,8 +1012,6 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1040,7 +1035,6 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1049,8 +1043,6 @@
       <c r="G4" t="n">
         <v>274</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1074,7 +1066,6 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1083,8 +1074,6 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1108,7 +1097,6 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1117,8 +1105,6 @@
       <c r="G6" t="n">
         <v>229.332</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1142,7 +1128,6 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1151,8 +1136,6 @@
       <c r="G7" t="n">
         <v>2630</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1176,7 +1159,6 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1185,8 +1167,6 @@
       <c r="G8" t="n">
         <v>800</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1210,7 +1190,6 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1219,8 +1198,6 @@
       <c r="G9" t="n">
         <v>274</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1244,7 +1221,6 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1253,8 +1229,6 @@
       <c r="G10" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1278,7 +1252,6 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1287,8 +1260,6 @@
       <c r="G11" t="n">
         <v>229.332</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1312,7 +1283,6 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1321,8 +1291,6 @@
       <c r="G12" t="n">
         <v>2630</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1346,7 +1314,6 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1355,8 +1322,6 @@
       <c r="G13" t="n">
         <v>800</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1380,7 +1345,6 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1389,8 +1353,6 @@
       <c r="G14" t="n">
         <v>274</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1414,7 +1376,6 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1423,8 +1384,6 @@
       <c r="G15" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1448,7 +1407,6 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1457,8 +1415,6 @@
       <c r="G16" t="n">
         <v>229.332</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1482,7 +1438,6 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1491,8 +1446,6 @@
       <c r="G17" t="n">
         <v>7.004</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1516,7 +1469,6 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1525,8 +1477,6 @@
       <c r="G18" t="n">
         <v>103</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1550,7 +1500,6 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1559,8 +1508,6 @@
       <c r="G19" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1584,7 +1531,6 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1593,8 +1539,6 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1618,7 +1562,6 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1627,8 +1570,6 @@
       <c r="G21" t="n">
         <v>20</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1652,7 +1593,6 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1661,8 +1601,6 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1686,7 +1624,6 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1695,8 +1632,6 @@
       <c r="G23" t="n">
         <v>60</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1720,7 +1655,6 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1729,8 +1663,6 @@
       <c r="G24" t="n">
         <v>2630</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1754,7 +1686,6 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1763,8 +1694,6 @@
       <c r="G25" t="n">
         <v>800</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1788,7 +1717,6 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1797,8 +1725,6 @@
       <c r="G26" t="n">
         <v>274</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1822,7 +1748,6 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1831,8 +1756,6 @@
       <c r="G27" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1856,7 +1779,6 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1865,8 +1787,6 @@
       <c r="G28" t="n">
         <v>229.332</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1890,7 +1810,6 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1899,8 +1818,6 @@
       <c r="G29" t="n">
         <v>7.004</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1924,7 +1841,6 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1933,8 +1849,6 @@
       <c r="G30" t="n">
         <v>103</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1958,7 +1872,6 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1967,8 +1880,6 @@
       <c r="G31" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1992,7 +1903,6 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2001,8 +1911,6 @@
       <c r="G32" t="n">
         <v>20</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2026,7 +1934,6 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2035,8 +1942,6 @@
       <c r="G33" t="n">
         <v>20</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2060,7 +1965,6 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2069,8 +1973,6 @@
       <c r="G34" t="n">
         <v>20</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2094,7 +1996,6 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2103,8 +2004,6 @@
       <c r="G35" t="n">
         <v>60</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2128,7 +2027,6 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2137,8 +2035,6 @@
       <c r="G36" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2162,7 +2058,6 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2171,8 +2066,6 @@
       <c r="G37" t="n">
         <v>61.8</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2196,7 +2089,6 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2205,8 +2097,6 @@
       <c r="G38" t="n">
         <v>54.384</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2230,7 +2120,6 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2239,8 +2128,6 @@
       <c r="G39" t="n">
         <v>2630</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2264,7 +2151,6 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2273,8 +2159,6 @@
       <c r="G40" t="n">
         <v>800</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2298,7 +2182,6 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2307,8 +2190,6 @@
       <c r="G41" t="n">
         <v>274</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2332,7 +2213,6 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2341,8 +2221,6 @@
       <c r="G42" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2366,7 +2244,6 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2375,8 +2252,6 @@
       <c r="G43" t="n">
         <v>229.332</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2400,7 +2275,6 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2409,8 +2283,6 @@
       <c r="G44" t="n">
         <v>7.004</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2434,7 +2306,6 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2443,8 +2314,6 @@
       <c r="G45" t="n">
         <v>103</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2468,7 +2337,6 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2477,8 +2345,6 @@
       <c r="G46" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2502,7 +2368,6 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2511,8 +2376,6 @@
       <c r="G47" t="n">
         <v>20</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2536,7 +2399,6 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2545,8 +2407,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2570,7 +2430,6 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2579,8 +2438,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2604,7 +2461,6 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2613,8 +2469,6 @@
       <c r="G50" t="n">
         <v>60</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2638,7 +2492,6 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2647,8 +2500,6 @@
       <c r="G51" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2672,7 +2523,6 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2681,8 +2531,6 @@
       <c r="G52" t="n">
         <v>61.8</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2706,7 +2554,6 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2715,8 +2562,6 @@
       <c r="G53" t="n">
         <v>54.384</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2740,7 +2585,6 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2749,8 +2593,6 @@
       <c r="G54" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2774,7 +2616,6 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2783,8 +2624,6 @@
       <c r="G55" t="n">
         <v>1613.23</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2808,7 +2647,6 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2817,8 +2655,6 @@
       <c r="G56" t="n">
         <v>645.48</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2842,7 +2678,6 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2851,8 +2686,6 @@
       <c r="G57" t="n">
         <v>500.5</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2876,7 +2709,6 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2885,8 +2717,6 @@
       <c r="G58" t="n">
         <v>283.5</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2910,7 +2740,6 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2919,8 +2748,6 @@
       <c r="G59" t="n">
         <v>250</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2944,7 +2771,6 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2953,8 +2779,6 @@
       <c r="G60" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2978,7 +2802,6 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2987,8 +2810,6 @@
       <c r="G61" t="n">
         <v>105.34</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3012,7 +2833,6 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -3021,8 +2841,6 @@
       <c r="G62" t="n">
         <v>96.899</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3046,7 +2864,6 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -3055,8 +2872,6 @@
       <c r="G63" t="n">
         <v>38.7596</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3080,7 +2895,6 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -3089,8 +2903,6 @@
       <c r="G64" t="n">
         <v>103</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3114,7 +2926,6 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -3123,8 +2934,6 @@
       <c r="G65" t="n">
         <v>51.5</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3148,7 +2957,6 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -3157,8 +2965,6 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3182,7 +2988,6 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -3191,8 +2996,6 @@
       <c r="G67" t="n">
         <v>61.8</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3216,7 +3019,6 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3225,8 +3027,6 @@
       <c r="G68" t="n">
         <v>54.384</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3250,7 +3050,6 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3259,8 +3058,6 @@
       <c r="G69" t="n">
         <v>50</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3284,7 +3081,6 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3293,8 +3089,6 @@
       <c r="G70" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3318,7 +3112,6 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3327,8 +3120,6 @@
       <c r="G71" t="n">
         <v>50</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3352,7 +3143,6 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3361,8 +3151,6 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3386,7 +3174,6 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3395,8 +3182,6 @@
       <c r="G73" t="n">
         <v>7.004</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3420,7 +3205,6 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3429,8 +3213,6 @@
       <c r="G74" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3454,7 +3236,6 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3463,8 +3244,6 @@
       <c r="G75" t="n">
         <v>27.4667</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3488,7 +3267,6 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3497,8 +3275,6 @@
       <c r="G76" t="n">
         <v>36.9083</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3522,7 +3298,6 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3531,8 +3306,6 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3556,7 +3329,6 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3565,8 +3337,6 @@
       <c r="G78" t="n">
         <v>60</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3590,7 +3360,6 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3599,8 +3368,6 @@
       <c r="G79" t="n">
         <v>20</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3624,7 +3391,6 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3633,8 +3399,6 @@
       <c r="G80" t="n">
         <v>60</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3658,7 +3422,6 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3667,8 +3430,6 @@
       <c r="G81" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3692,7 +3453,6 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3701,8 +3461,6 @@
       <c r="G82" t="n">
         <v>20</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3726,7 +3484,6 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3735,8 +3492,6 @@
       <c r="G83" t="n">
         <v>20</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3760,7 +3515,6 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3769,8 +3523,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3794,7 +3546,6 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3803,8 +3554,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3828,7 +3577,6 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3837,8 +3585,6 @@
       <c r="G86" t="n">
         <v>20</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3862,7 +3608,6 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3871,8 +3616,6 @@
       <c r="G87" t="n">
         <v>20</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3896,7 +3639,6 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3905,11 +3647,3229 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>上一时点</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量87条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-933.7074</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>丰利财富</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-66.66800000000001</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>274</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>274</v>
+      </c>
+      <c r="G6" t="n">
+        <v>274</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>800</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F7" t="n">
+        <v>825</v>
+      </c>
+      <c r="G7" t="n">
+        <v>800</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G8" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-669.3701</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>274</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>274</v>
+      </c>
+      <c r="G12" t="n">
+        <v>274</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>800</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>825</v>
+      </c>
+      <c r="G13" t="n">
+        <v>800</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G14" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>103</v>
+      </c>
+      <c r="F15" t="n">
+        <v>103</v>
+      </c>
+      <c r="G15" t="n">
+        <v>103</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>60</v>
+      </c>
+      <c r="F16" t="n">
+        <v>60</v>
+      </c>
+      <c r="G16" t="n">
+        <v>60</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>20</v>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F22" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="G22" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="E24" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F24" t="n">
+        <v>5198.0447</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4635</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-563.0447</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G25" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F26" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="G26" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>274</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>274</v>
+      </c>
+      <c r="G27" t="n">
+        <v>274</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>800</v>
+      </c>
+      <c r="E28" t="n">
+        <v>25</v>
+      </c>
+      <c r="F28" t="n">
+        <v>825</v>
+      </c>
+      <c r="G28" t="n">
+        <v>800</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G29" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>103</v>
+      </c>
+      <c r="E30" t="n">
+        <v>103</v>
+      </c>
+      <c r="F30" t="n">
+        <v>206</v>
+      </c>
+      <c r="G30" t="n">
+        <v>103</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>60</v>
+      </c>
+      <c r="E31" t="n">
+        <v>60</v>
+      </c>
+      <c r="F31" t="n">
+        <v>120</v>
+      </c>
+      <c r="G31" t="n">
+        <v>60</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F32" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="G32" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" t="n">
+        <v>20</v>
+      </c>
+      <c r="F36" t="n">
+        <v>40</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20</v>
+      </c>
+      <c r="F37" t="n">
+        <v>40</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="E38" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F38" t="n">
+        <v>68.6666</v>
+      </c>
+      <c r="G38" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-34.3333</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="n">
+        <v>40</v>
+      </c>
+      <c r="G39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>4635</v>
+      </c>
+      <c r="E40" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F40" t="n">
+        <v>5568.7074</v>
+      </c>
+      <c r="G40" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-820.6586</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E41" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F41" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="G41" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="E42" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F42" t="n">
+        <v>108.768</v>
+      </c>
+      <c r="G42" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-54.384</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>274</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>274</v>
+      </c>
+      <c r="G43" t="n">
+        <v>274</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>800</v>
+      </c>
+      <c r="E44" t="n">
+        <v>25</v>
+      </c>
+      <c r="F44" t="n">
+        <v>825</v>
+      </c>
+      <c r="G44" t="n">
+        <v>800</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G45" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>103</v>
+      </c>
+      <c r="E46" t="n">
+        <v>103</v>
+      </c>
+      <c r="F46" t="n">
+        <v>206</v>
+      </c>
+      <c r="G46" t="n">
+        <v>103</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>60</v>
+      </c>
+      <c r="E47" t="n">
+        <v>60</v>
+      </c>
+      <c r="F47" t="n">
+        <v>120</v>
+      </c>
+      <c r="G47" t="n">
+        <v>60</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="E48" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F48" t="n">
+        <v>508.9574</v>
+      </c>
+      <c r="G48" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-254.4787</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E49" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G50" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G51" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>20</v>
+      </c>
+      <c r="E52" t="n">
+        <v>20</v>
+      </c>
+      <c r="F52" t="n">
+        <v>40</v>
+      </c>
+      <c r="G52" t="n">
+        <v>20</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>20</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" t="n">
+        <v>40</v>
+      </c>
+      <c r="G53" t="n">
+        <v>20</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>火炬电子</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="F54" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="G54" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="E55" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F55" t="n">
+        <v>68.6666</v>
+      </c>
+      <c r="G55" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-34.3333</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>20</v>
+      </c>
+      <c r="E56" t="n">
+        <v>20</v>
+      </c>
+      <c r="F56" t="n">
+        <v>40</v>
+      </c>
+      <c r="G56" t="n">
+        <v>20</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="E57" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F57" t="n">
+        <v>5681.7562</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4880.2539</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-801.5023</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>东方富海</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>250</v>
+      </c>
+      <c r="H59" t="n">
+        <v>250</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>中小企业基金</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>38.7596</v>
+      </c>
+      <c r="F60" t="n">
+        <v>38.7596</v>
+      </c>
+      <c r="G60" t="n">
+        <v>38.7596</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="E61" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F61" t="n">
+        <v>108.768</v>
+      </c>
+      <c r="G61" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-54.384</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>临港投资</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>27.4667</v>
+      </c>
+      <c r="H62" t="n">
+        <v>27.4667</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>274</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>274</v>
+      </c>
+      <c r="G63" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-168.66</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>余满芬</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>20</v>
+      </c>
+      <c r="H64" t="n">
+        <v>20</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>800</v>
+      </c>
+      <c r="E65" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" t="n">
+        <v>825</v>
+      </c>
+      <c r="G65" t="n">
+        <v>645.48</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-179.52</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G66" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>271.168</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>103</v>
+      </c>
+      <c r="E67" t="n">
+        <v>103</v>
+      </c>
+      <c r="F67" t="n">
+        <v>206</v>
+      </c>
+      <c r="G67" t="n">
+        <v>103</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>厦门西堤</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="F68" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="G68" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>60</v>
+      </c>
+      <c r="E69" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" t="n">
+        <v>120</v>
+      </c>
+      <c r="G69" t="n">
+        <v>60</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="E70" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F70" t="n">
+        <v>508.9574</v>
+      </c>
+      <c r="G70" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-254.4787</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G71" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G72" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>富海深湾</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>50</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>富海节能</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>崔振南</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="n">
+        <v>20</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>昆山红土</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>50</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1613.23</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-1016.77</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>20</v>
+      </c>
+      <c r="E78" t="n">
+        <v>20</v>
+      </c>
+      <c r="F78" t="n">
+        <v>40</v>
+      </c>
+      <c r="G78" t="n">
+        <v>20</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>20</v>
+      </c>
+      <c r="E79" t="n">
+        <v>20</v>
+      </c>
+      <c r="F79" t="n">
+        <v>40</v>
+      </c>
+      <c r="G79" t="n">
+        <v>60</v>
+      </c>
+      <c r="H79" t="n">
+        <v>20</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>沈笑彦</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" t="n">
+        <v>20</v>
+      </c>
+      <c r="H80" t="n">
+        <v>20</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>深创投</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>50</v>
+      </c>
+      <c r="H81" t="n">
+        <v>50</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>湘裕君源</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>15.9535</v>
+      </c>
+      <c r="H82" t="n">
+        <v>15.9535</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,6 +972,7 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -981,6 +981,8 @@
       <c r="G2" t="n">
         <v>2630</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1004,6 +1006,7 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1012,6 +1015,8 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1035,6 +1040,7 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1043,6 +1049,8 @@
       <c r="G4" t="n">
         <v>274</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1066,6 +1074,7 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1074,6 +1083,8 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1097,6 +1108,7 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1105,6 +1117,8 @@
       <c r="G6" t="n">
         <v>229.332</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1128,6 +1142,7 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1136,6 +1151,8 @@
       <c r="G7" t="n">
         <v>2630</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1159,6 +1176,7 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1167,6 +1185,8 @@
       <c r="G8" t="n">
         <v>800</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1190,6 +1210,7 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1198,6 +1219,8 @@
       <c r="G9" t="n">
         <v>274</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1221,6 +1244,7 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1229,6 +1253,8 @@
       <c r="G10" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1252,6 +1278,7 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1260,6 +1287,8 @@
       <c r="G11" t="n">
         <v>229.332</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1283,6 +1312,7 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1291,6 +1321,8 @@
       <c r="G12" t="n">
         <v>2630</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1314,6 +1346,7 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1322,6 +1355,8 @@
       <c r="G13" t="n">
         <v>800</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1345,6 +1380,7 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1353,6 +1389,8 @@
       <c r="G14" t="n">
         <v>274</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1376,6 +1414,7 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1384,6 +1423,8 @@
       <c r="G15" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1407,6 +1448,7 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1415,6 +1457,8 @@
       <c r="G16" t="n">
         <v>229.332</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1438,6 +1482,7 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1446,6 +1491,8 @@
       <c r="G17" t="n">
         <v>7.004</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1469,6 +1516,7 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1477,6 +1525,8 @@
       <c r="G18" t="n">
         <v>103</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1500,6 +1550,7 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1508,6 +1559,8 @@
       <c r="G19" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1531,6 +1584,7 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1539,6 +1593,8 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1562,6 +1618,7 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1570,6 +1627,8 @@
       <c r="G21" t="n">
         <v>20</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1593,6 +1652,7 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1601,6 +1661,8 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1624,6 +1686,7 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1632,6 +1695,8 @@
       <c r="G23" t="n">
         <v>60</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1655,6 +1720,7 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1663,6 +1729,8 @@
       <c r="G24" t="n">
         <v>2630</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1686,6 +1754,7 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1694,6 +1763,8 @@
       <c r="G25" t="n">
         <v>800</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1717,6 +1788,7 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1725,6 +1797,8 @@
       <c r="G26" t="n">
         <v>274</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1748,6 +1822,7 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1756,6 +1831,8 @@
       <c r="G27" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1779,6 +1856,7 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1787,6 +1865,8 @@
       <c r="G28" t="n">
         <v>229.332</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1810,6 +1890,7 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1818,6 +1899,8 @@
       <c r="G29" t="n">
         <v>7.004</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1841,6 +1924,7 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1849,6 +1933,8 @@
       <c r="G30" t="n">
         <v>103</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1872,6 +1958,7 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1880,6 +1967,8 @@
       <c r="G31" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1903,6 +1992,7 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1911,6 +2001,8 @@
       <c r="G32" t="n">
         <v>20</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1934,6 +2026,7 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1942,6 +2035,8 @@
       <c r="G33" t="n">
         <v>20</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1965,6 +2060,7 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1973,6 +2069,8 @@
       <c r="G34" t="n">
         <v>20</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1996,6 +2094,7 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2004,6 +2103,8 @@
       <c r="G35" t="n">
         <v>60</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2027,6 +2128,7 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2035,6 +2137,8 @@
       <c r="G36" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2058,6 +2162,7 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2066,6 +2171,8 @@
       <c r="G37" t="n">
         <v>61.8</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2089,6 +2196,7 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2097,6 +2205,8 @@
       <c r="G38" t="n">
         <v>54.384</v>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2120,6 +2230,7 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2128,6 +2239,8 @@
       <c r="G39" t="n">
         <v>2630</v>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2151,6 +2264,7 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2159,6 +2273,8 @@
       <c r="G40" t="n">
         <v>800</v>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2182,6 +2298,7 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2190,6 +2307,8 @@
       <c r="G41" t="n">
         <v>274</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2213,6 +2332,7 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2221,6 +2341,8 @@
       <c r="G42" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2244,6 +2366,7 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2252,6 +2375,8 @@
       <c r="G43" t="n">
         <v>229.332</v>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2275,6 +2400,7 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2283,6 +2409,8 @@
       <c r="G44" t="n">
         <v>7.004</v>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2306,6 +2434,7 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2314,6 +2443,8 @@
       <c r="G45" t="n">
         <v>103</v>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2337,6 +2468,7 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2345,6 +2477,8 @@
       <c r="G46" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2368,6 +2502,7 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2376,6 +2511,8 @@
       <c r="G47" t="n">
         <v>20</v>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2399,6 +2536,7 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2407,6 +2545,8 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2430,6 +2570,7 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2438,6 +2579,8 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2461,6 +2604,7 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2469,6 +2613,8 @@
       <c r="G50" t="n">
         <v>60</v>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2492,6 +2638,7 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2500,6 +2647,8 @@
       <c r="G51" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2523,6 +2672,7 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2531,6 +2681,8 @@
       <c r="G52" t="n">
         <v>61.8</v>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2554,6 +2706,7 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2562,6 +2715,8 @@
       <c r="G53" t="n">
         <v>54.384</v>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2585,6 +2740,7 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2593,6 +2749,8 @@
       <c r="G54" t="n">
         <v>113.0488</v>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2616,6 +2774,7 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2624,6 +2783,8 @@
       <c r="G55" t="n">
         <v>1613.23</v>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2647,6 +2808,7 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2655,6 +2817,8 @@
       <c r="G56" t="n">
         <v>645.48</v>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2678,6 +2842,7 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2686,6 +2851,8 @@
       <c r="G57" t="n">
         <v>500.5</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2709,6 +2876,7 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2717,6 +2885,8 @@
       <c r="G58" t="n">
         <v>283.5</v>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2740,6 +2910,7 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2748,6 +2919,8 @@
       <c r="G59" t="n">
         <v>250</v>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2771,6 +2944,7 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2779,6 +2953,8 @@
       <c r="G60" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2802,6 +2978,7 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2810,6 +2987,8 @@
       <c r="G61" t="n">
         <v>105.34</v>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2833,6 +3012,7 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -2841,6 +3021,8 @@
       <c r="G62" t="n">
         <v>96.899</v>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2864,6 +3046,7 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -2872,6 +3055,8 @@
       <c r="G63" t="n">
         <v>38.7596</v>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2895,6 +3080,7 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2903,6 +3089,8 @@
       <c r="G64" t="n">
         <v>103</v>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2926,6 +3114,7 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -2934,6 +3123,8 @@
       <c r="G65" t="n">
         <v>51.5</v>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2957,6 +3148,7 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -2965,6 +3157,8 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2988,6 +3182,7 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2996,6 +3191,8 @@
       <c r="G67" t="n">
         <v>61.8</v>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3019,6 +3216,7 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3027,6 +3225,8 @@
       <c r="G68" t="n">
         <v>54.384</v>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3050,6 +3250,7 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3058,6 +3259,8 @@
       <c r="G69" t="n">
         <v>50</v>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3081,6 +3284,7 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3089,6 +3293,8 @@
       <c r="G70" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3112,6 +3318,7 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3120,6 +3327,8 @@
       <c r="G71" t="n">
         <v>50</v>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3143,6 +3352,7 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3151,6 +3361,8 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3174,6 +3386,7 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3182,6 +3395,8 @@
       <c r="G73" t="n">
         <v>7.004</v>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3205,6 +3420,7 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3213,6 +3429,8 @@
       <c r="G74" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3236,6 +3454,7 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3244,6 +3463,8 @@
       <c r="G75" t="n">
         <v>27.4667</v>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3267,6 +3488,7 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3275,6 +3497,8 @@
       <c r="G76" t="n">
         <v>36.9083</v>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3298,6 +3522,7 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3306,6 +3531,8 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3329,6 +3556,7 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3337,6 +3565,8 @@
       <c r="G78" t="n">
         <v>60</v>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3360,6 +3590,7 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3368,6 +3599,8 @@
       <c r="G79" t="n">
         <v>20</v>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3391,6 +3624,7 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3399,6 +3633,8 @@
       <c r="G80" t="n">
         <v>60</v>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3422,6 +3658,7 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3430,6 +3667,8 @@
       <c r="G81" t="n">
         <v>113.0488</v>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3453,6 +3692,7 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3461,6 +3701,8 @@
       <c r="G82" t="n">
         <v>20</v>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3484,6 +3726,7 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3492,6 +3735,8 @@
       <c r="G83" t="n">
         <v>20</v>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3515,6 +3760,7 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3523,6 +3769,8 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3546,6 +3794,7 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3554,6 +3803,8 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3577,6 +3828,7 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3585,6 +3837,8 @@
       <c r="G86" t="n">
         <v>20</v>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3608,6 +3862,7 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3616,6 +3871,8 @@
       <c r="G87" t="n">
         <v>20</v>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3639,6 +3896,7 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3647,3229 +3905,11 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J82"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量87条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-933.7074</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>丰利财富</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-66.66800000000001</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>274</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>274</v>
-      </c>
-      <c r="G6" t="n">
-        <v>274</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>800</v>
-      </c>
-      <c r="E7" t="n">
-        <v>25</v>
-      </c>
-      <c r="F7" t="n">
-        <v>825</v>
-      </c>
-      <c r="G7" t="n">
-        <v>800</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G8" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G10" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E11" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F11" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-669.3701</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>274</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>274</v>
-      </c>
-      <c r="G12" t="n">
-        <v>274</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>800</v>
-      </c>
-      <c r="E13" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" t="n">
-        <v>825</v>
-      </c>
-      <c r="G13" t="n">
-        <v>800</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G14" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>103</v>
-      </c>
-      <c r="F15" t="n">
-        <v>103</v>
-      </c>
-      <c r="G15" t="n">
-        <v>103</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>60</v>
-      </c>
-      <c r="F16" t="n">
-        <v>60</v>
-      </c>
-      <c r="G16" t="n">
-        <v>60</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F17" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="G17" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>20</v>
-      </c>
-      <c r="F20" t="n">
-        <v>20</v>
-      </c>
-      <c r="G20" t="n">
-        <v>20</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>20</v>
-      </c>
-      <c r="F21" t="n">
-        <v>20</v>
-      </c>
-      <c r="G21" t="n">
-        <v>20</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F22" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="G22" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23" t="n">
-        <v>20</v>
-      </c>
-      <c r="G23" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="E24" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F24" t="n">
-        <v>5198.0447</v>
-      </c>
-      <c r="G24" t="n">
-        <v>4635</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-563.0447</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F25" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F26" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="G26" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>274</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>274</v>
-      </c>
-      <c r="G27" t="n">
-        <v>274</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>800</v>
-      </c>
-      <c r="E28" t="n">
-        <v>25</v>
-      </c>
-      <c r="F28" t="n">
-        <v>825</v>
-      </c>
-      <c r="G28" t="n">
-        <v>800</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G29" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>103</v>
-      </c>
-      <c r="E30" t="n">
-        <v>103</v>
-      </c>
-      <c r="F30" t="n">
-        <v>206</v>
-      </c>
-      <c r="G30" t="n">
-        <v>103</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>60</v>
-      </c>
-      <c r="E31" t="n">
-        <v>60</v>
-      </c>
-      <c r="F31" t="n">
-        <v>120</v>
-      </c>
-      <c r="G31" t="n">
-        <v>60</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F32" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="G32" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E33" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F33" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G33" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G34" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>20</v>
-      </c>
-      <c r="E36" t="n">
-        <v>20</v>
-      </c>
-      <c r="F36" t="n">
-        <v>40</v>
-      </c>
-      <c r="G36" t="n">
-        <v>20</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>20</v>
-      </c>
-      <c r="E37" t="n">
-        <v>20</v>
-      </c>
-      <c r="F37" t="n">
-        <v>40</v>
-      </c>
-      <c r="G37" t="n">
-        <v>20</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="E38" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F38" t="n">
-        <v>68.6666</v>
-      </c>
-      <c r="G38" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-34.3333</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E39" t="n">
-        <v>20</v>
-      </c>
-      <c r="F39" t="n">
-        <v>40</v>
-      </c>
-      <c r="G39" t="n">
-        <v>20</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4635</v>
-      </c>
-      <c r="E40" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F40" t="n">
-        <v>5568.7074</v>
-      </c>
-      <c r="G40" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-820.6586</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="E41" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F41" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="G41" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-61.8</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="E42" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F42" t="n">
-        <v>108.768</v>
-      </c>
-      <c r="G42" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-54.384</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>274</v>
-      </c>
-      <c r="E43" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>274</v>
-      </c>
-      <c r="G43" t="n">
-        <v>274</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>800</v>
-      </c>
-      <c r="E44" t="n">
-        <v>25</v>
-      </c>
-      <c r="F44" t="n">
-        <v>825</v>
-      </c>
-      <c r="G44" t="n">
-        <v>800</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G45" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>103</v>
-      </c>
-      <c r="E46" t="n">
-        <v>103</v>
-      </c>
-      <c r="F46" t="n">
-        <v>206</v>
-      </c>
-      <c r="G46" t="n">
-        <v>103</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>60</v>
-      </c>
-      <c r="E47" t="n">
-        <v>60</v>
-      </c>
-      <c r="F47" t="n">
-        <v>120</v>
-      </c>
-      <c r="G47" t="n">
-        <v>60</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="E48" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F48" t="n">
-        <v>508.9574</v>
-      </c>
-      <c r="G48" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-254.4787</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E49" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F49" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G49" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G50" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>20</v>
-      </c>
-      <c r="E52" t="n">
-        <v>20</v>
-      </c>
-      <c r="F52" t="n">
-        <v>40</v>
-      </c>
-      <c r="G52" t="n">
-        <v>20</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>20</v>
-      </c>
-      <c r="E53" t="n">
-        <v>20</v>
-      </c>
-      <c r="F53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G53" t="n">
-        <v>20</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>火炬电子</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="F54" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="G54" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="E55" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F55" t="n">
-        <v>68.6666</v>
-      </c>
-      <c r="G55" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-34.3333</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>20</v>
-      </c>
-      <c r="E56" t="n">
-        <v>20</v>
-      </c>
-      <c r="F56" t="n">
-        <v>40</v>
-      </c>
-      <c r="G56" t="n">
-        <v>20</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="E57" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F57" t="n">
-        <v>5681.7562</v>
-      </c>
-      <c r="G57" t="n">
-        <v>4880.2539</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-801.5023</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="E58" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F58" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="G58" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-61.8</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>东方富海</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>250</v>
-      </c>
-      <c r="H59" t="n">
-        <v>250</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>中小企业基金</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>38.7596</v>
-      </c>
-      <c r="F60" t="n">
-        <v>38.7596</v>
-      </c>
-      <c r="G60" t="n">
-        <v>38.7596</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="E61" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F61" t="n">
-        <v>108.768</v>
-      </c>
-      <c r="G61" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-54.384</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>临港投资</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>27.4667</v>
-      </c>
-      <c r="H62" t="n">
-        <v>27.4667</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>274</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>274</v>
-      </c>
-      <c r="G63" t="n">
-        <v>105.34</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-168.66</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>余满芬</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>20</v>
-      </c>
-      <c r="H64" t="n">
-        <v>20</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>800</v>
-      </c>
-      <c r="E65" t="n">
-        <v>25</v>
-      </c>
-      <c r="F65" t="n">
-        <v>825</v>
-      </c>
-      <c r="G65" t="n">
-        <v>645.48</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-179.52</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G66" t="n">
-        <v>500.5</v>
-      </c>
-      <c r="H66" t="n">
-        <v>271.168</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>103</v>
-      </c>
-      <c r="E67" t="n">
-        <v>103</v>
-      </c>
-      <c r="F67" t="n">
-        <v>206</v>
-      </c>
-      <c r="G67" t="n">
-        <v>103</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>厦门西堤</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="F68" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="G68" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>60</v>
-      </c>
-      <c r="E69" t="n">
-        <v>60</v>
-      </c>
-      <c r="F69" t="n">
-        <v>120</v>
-      </c>
-      <c r="G69" t="n">
-        <v>60</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="E70" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F70" t="n">
-        <v>508.9574</v>
-      </c>
-      <c r="G70" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-254.4787</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E71" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F71" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G71" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G72" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>富海深湾</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>50</v>
-      </c>
-      <c r="H73" t="n">
-        <v>50</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>富海节能</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H74" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>崔振南</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>20</v>
-      </c>
-      <c r="H75" t="n">
-        <v>20</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>昆山红土</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>50</v>
-      </c>
-      <c r="H76" t="n">
-        <v>50</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1613.23</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-1016.77</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>20</v>
-      </c>
-      <c r="E78" t="n">
-        <v>20</v>
-      </c>
-      <c r="F78" t="n">
-        <v>40</v>
-      </c>
-      <c r="G78" t="n">
-        <v>20</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>20</v>
-      </c>
-      <c r="E79" t="n">
-        <v>20</v>
-      </c>
-      <c r="F79" t="n">
-        <v>40</v>
-      </c>
-      <c r="G79" t="n">
-        <v>60</v>
-      </c>
-      <c r="H79" t="n">
-        <v>20</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>沈笑彦</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" t="n">
-        <v>20</v>
-      </c>
-      <c r="H80" t="n">
-        <v>20</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>深创投</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G81" t="n">
-        <v>50</v>
-      </c>
-      <c r="H81" t="n">
-        <v>50</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>湘裕君源</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" t="n">
-        <v>15.9535</v>
-      </c>
-      <c r="H82" t="n">
-        <v>15.9535</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>新增</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -972,7 +973,6 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -981,8 +981,6 @@
       <c r="G2" t="n">
         <v>2630</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1006,7 +1004,6 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1015,8 +1012,6 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1040,7 +1035,6 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1049,8 +1043,6 @@
       <c r="G4" t="n">
         <v>274</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1074,7 +1066,6 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1083,8 +1074,6 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1108,7 +1097,6 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1117,8 +1105,6 @@
       <c r="G6" t="n">
         <v>229.332</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1142,7 +1128,6 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1151,8 +1136,6 @@
       <c r="G7" t="n">
         <v>2630</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1176,7 +1159,6 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1185,8 +1167,6 @@
       <c r="G8" t="n">
         <v>800</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1210,7 +1190,6 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1219,8 +1198,6 @@
       <c r="G9" t="n">
         <v>274</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1244,7 +1221,6 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1253,8 +1229,6 @@
       <c r="G10" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1278,7 +1252,6 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1287,8 +1260,6 @@
       <c r="G11" t="n">
         <v>229.332</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1312,7 +1283,6 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1321,8 +1291,6 @@
       <c r="G12" t="n">
         <v>2630</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1346,7 +1314,6 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1355,8 +1322,6 @@
       <c r="G13" t="n">
         <v>800</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1380,7 +1345,6 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1389,8 +1353,6 @@
       <c r="G14" t="n">
         <v>274</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1414,7 +1376,6 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1423,8 +1384,6 @@
       <c r="G15" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1448,7 +1407,6 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1457,8 +1415,6 @@
       <c r="G16" t="n">
         <v>229.332</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1482,7 +1438,6 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1491,8 +1446,6 @@
       <c r="G17" t="n">
         <v>7.004</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1516,7 +1469,6 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1525,8 +1477,6 @@
       <c r="G18" t="n">
         <v>103</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1550,7 +1500,6 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1559,8 +1508,6 @@
       <c r="G19" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1584,7 +1531,6 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1593,8 +1539,6 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1618,7 +1562,6 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1627,8 +1570,6 @@
       <c r="G21" t="n">
         <v>20</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1652,7 +1593,6 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1661,8 +1601,6 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1686,7 +1624,6 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1695,8 +1632,6 @@
       <c r="G23" t="n">
         <v>60</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1720,7 +1655,6 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1729,8 +1663,6 @@
       <c r="G24" t="n">
         <v>2630</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1754,7 +1686,6 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1763,8 +1694,6 @@
       <c r="G25" t="n">
         <v>800</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1788,7 +1717,6 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1797,8 +1725,6 @@
       <c r="G26" t="n">
         <v>274</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1822,7 +1748,6 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1831,8 +1756,6 @@
       <c r="G27" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1856,7 +1779,6 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1865,8 +1787,6 @@
       <c r="G28" t="n">
         <v>229.332</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1890,7 +1810,6 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1899,8 +1818,6 @@
       <c r="G29" t="n">
         <v>7.004</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1924,7 +1841,6 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1933,8 +1849,6 @@
       <c r="G30" t="n">
         <v>103</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1958,7 +1872,6 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1967,8 +1880,6 @@
       <c r="G31" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1992,7 +1903,6 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2001,8 +1911,6 @@
       <c r="G32" t="n">
         <v>20</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2026,7 +1934,6 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2035,8 +1942,6 @@
       <c r="G33" t="n">
         <v>20</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2060,7 +1965,6 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2069,8 +1973,6 @@
       <c r="G34" t="n">
         <v>20</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2094,7 +1996,6 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2103,8 +2004,6 @@
       <c r="G35" t="n">
         <v>60</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2128,7 +2027,6 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2137,8 +2035,6 @@
       <c r="G36" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2162,7 +2058,6 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2171,8 +2066,6 @@
       <c r="G37" t="n">
         <v>61.8</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2196,7 +2089,6 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2205,8 +2097,6 @@
       <c r="G38" t="n">
         <v>54.384</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2230,7 +2120,6 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2239,8 +2128,6 @@
       <c r="G39" t="n">
         <v>2630</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2264,7 +2151,6 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2273,8 +2159,6 @@
       <c r="G40" t="n">
         <v>800</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2298,7 +2182,6 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2307,8 +2190,6 @@
       <c r="G41" t="n">
         <v>274</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2332,7 +2213,6 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2341,8 +2221,6 @@
       <c r="G42" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2366,7 +2244,6 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2375,8 +2252,6 @@
       <c r="G43" t="n">
         <v>229.332</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2400,7 +2275,6 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2409,8 +2283,6 @@
       <c r="G44" t="n">
         <v>7.004</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2434,7 +2306,6 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2443,8 +2314,6 @@
       <c r="G45" t="n">
         <v>103</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2468,7 +2337,6 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2477,8 +2345,6 @@
       <c r="G46" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2502,7 +2368,6 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2511,8 +2376,6 @@
       <c r="G47" t="n">
         <v>20</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2536,7 +2399,6 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2545,8 +2407,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2570,7 +2430,6 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2579,8 +2438,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2604,7 +2461,6 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2613,8 +2469,6 @@
       <c r="G50" t="n">
         <v>60</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2638,7 +2492,6 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2647,8 +2500,6 @@
       <c r="G51" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2672,7 +2523,6 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2681,8 +2531,6 @@
       <c r="G52" t="n">
         <v>61.8</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2706,7 +2554,6 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2715,8 +2562,6 @@
       <c r="G53" t="n">
         <v>54.384</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2740,7 +2585,6 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2749,8 +2593,6 @@
       <c r="G54" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2774,7 +2616,6 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2783,8 +2624,6 @@
       <c r="G55" t="n">
         <v>1613.23</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2808,7 +2647,6 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2817,8 +2655,6 @@
       <c r="G56" t="n">
         <v>645.48</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2842,7 +2678,6 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2851,8 +2686,6 @@
       <c r="G57" t="n">
         <v>500.5</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2876,7 +2709,6 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2885,8 +2717,6 @@
       <c r="G58" t="n">
         <v>283.5</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2910,7 +2740,6 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2919,8 +2748,6 @@
       <c r="G59" t="n">
         <v>250</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2944,7 +2771,6 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2953,8 +2779,6 @@
       <c r="G60" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2978,7 +2802,6 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2987,8 +2810,6 @@
       <c r="G61" t="n">
         <v>105.34</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3012,7 +2833,6 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -3021,8 +2841,6 @@
       <c r="G62" t="n">
         <v>96.899</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3046,7 +2864,6 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -3055,8 +2872,6 @@
       <c r="G63" t="n">
         <v>38.7596</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3080,7 +2895,6 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -3089,8 +2903,6 @@
       <c r="G64" t="n">
         <v>103</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3114,7 +2926,6 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -3123,8 +2934,6 @@
       <c r="G65" t="n">
         <v>51.5</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3148,7 +2957,6 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -3157,8 +2965,6 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3182,7 +2988,6 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -3191,8 +2996,6 @@
       <c r="G67" t="n">
         <v>61.8</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3216,7 +3019,6 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3225,8 +3027,6 @@
       <c r="G68" t="n">
         <v>54.384</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3250,7 +3050,6 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3259,8 +3058,6 @@
       <c r="G69" t="n">
         <v>50</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3284,7 +3081,6 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3293,8 +3089,6 @@
       <c r="G70" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3318,7 +3112,6 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3327,8 +3120,6 @@
       <c r="G71" t="n">
         <v>50</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3352,7 +3143,6 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3361,8 +3151,6 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3386,7 +3174,6 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3395,8 +3182,6 @@
       <c r="G73" t="n">
         <v>7.004</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3420,7 +3205,6 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3429,8 +3213,6 @@
       <c r="G74" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3454,7 +3236,6 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3463,8 +3244,6 @@
       <c r="G75" t="n">
         <v>27.4667</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3488,7 +3267,6 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3497,8 +3275,6 @@
       <c r="G76" t="n">
         <v>36.9083</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3522,7 +3298,6 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3531,8 +3306,6 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3556,7 +3329,6 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3565,8 +3337,6 @@
       <c r="G78" t="n">
         <v>60</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3590,7 +3360,6 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3599,8 +3368,6 @@
       <c r="G79" t="n">
         <v>20</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3624,7 +3391,6 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3633,8 +3399,6 @@
       <c r="G80" t="n">
         <v>60</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3658,7 +3422,6 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3667,8 +3430,6 @@
       <c r="G81" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3692,7 +3453,6 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3701,8 +3461,6 @@
       <c r="G82" t="n">
         <v>20</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3726,7 +3484,6 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3735,8 +3492,6 @@
       <c r="G83" t="n">
         <v>20</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3760,7 +3515,6 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3769,8 +3523,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3794,7 +3546,6 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3803,8 +3554,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3828,7 +3577,6 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3837,8 +3585,6 @@
       <c r="G86" t="n">
         <v>20</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3862,7 +3608,6 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3871,8 +3616,6 @@
       <c r="G87" t="n">
         <v>20</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3896,7 +3639,6 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3905,12 +3647,322 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本次变化</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>预期值</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>PDF值</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>差额</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段类型+非空检查通过</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量87条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在+类型检查通过</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-933.7074</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-669.3701</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="G6" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5198.0447</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4635</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-563.0447</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>4635</v>
+      </c>
+      <c r="G7" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5568.7074</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-820.6586</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="G8" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5681.7562</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4880.2539</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-801.5023</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,6 +972,7 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -981,6 +981,8 @@
       <c r="G2" t="n">
         <v>2630</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1004,6 +1006,7 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1012,6 +1015,8 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1035,6 +1040,7 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1043,6 +1049,8 @@
       <c r="G4" t="n">
         <v>274</v>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1066,6 +1074,7 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1074,6 +1083,8 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1097,6 +1108,7 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1105,6 +1117,8 @@
       <c r="G6" t="n">
         <v>229.332</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1128,6 +1142,7 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1136,6 +1151,8 @@
       <c r="G7" t="n">
         <v>2630</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1159,6 +1176,7 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1167,6 +1185,8 @@
       <c r="G8" t="n">
         <v>800</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1190,6 +1210,7 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1198,6 +1219,8 @@
       <c r="G9" t="n">
         <v>274</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1221,6 +1244,7 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1229,6 +1253,8 @@
       <c r="G10" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1252,6 +1278,7 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1260,6 +1287,8 @@
       <c r="G11" t="n">
         <v>229.332</v>
       </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1283,6 +1312,7 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1291,6 +1321,8 @@
       <c r="G12" t="n">
         <v>2630</v>
       </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1314,6 +1346,7 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1322,6 +1355,8 @@
       <c r="G13" t="n">
         <v>800</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1345,6 +1380,7 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1353,6 +1389,8 @@
       <c r="G14" t="n">
         <v>274</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1376,6 +1414,7 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1384,6 +1423,8 @@
       <c r="G15" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1407,6 +1448,7 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1415,6 +1457,8 @@
       <c r="G16" t="n">
         <v>229.332</v>
       </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1438,6 +1482,7 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1446,6 +1491,8 @@
       <c r="G17" t="n">
         <v>7.004</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1469,6 +1516,7 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1477,6 +1525,8 @@
       <c r="G18" t="n">
         <v>103</v>
       </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1500,6 +1550,7 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1508,6 +1559,8 @@
       <c r="G19" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1531,6 +1584,7 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1539,6 +1593,8 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1562,6 +1618,7 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1570,6 +1627,8 @@
       <c r="G21" t="n">
         <v>20</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1593,6 +1652,7 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1601,6 +1661,8 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1624,6 +1686,7 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1632,6 +1695,8 @@
       <c r="G23" t="n">
         <v>60</v>
       </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1655,6 +1720,7 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1663,6 +1729,8 @@
       <c r="G24" t="n">
         <v>2630</v>
       </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1686,6 +1754,7 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1694,6 +1763,8 @@
       <c r="G25" t="n">
         <v>800</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1717,6 +1788,7 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1725,6 +1797,8 @@
       <c r="G26" t="n">
         <v>274</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1748,6 +1822,7 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1756,6 +1831,8 @@
       <c r="G27" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1779,6 +1856,7 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1787,6 +1865,8 @@
       <c r="G28" t="n">
         <v>229.332</v>
       </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1810,6 +1890,7 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1818,6 +1899,8 @@
       <c r="G29" t="n">
         <v>7.004</v>
       </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1841,6 +1924,7 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1849,6 +1933,8 @@
       <c r="G30" t="n">
         <v>103</v>
       </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1872,6 +1958,7 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1880,6 +1967,8 @@
       <c r="G31" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1903,6 +1992,7 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1911,6 +2001,8 @@
       <c r="G32" t="n">
         <v>20</v>
       </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1934,6 +2026,7 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1942,6 +2035,8 @@
       <c r="G33" t="n">
         <v>20</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1965,6 +2060,7 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1973,6 +2069,8 @@
       <c r="G34" t="n">
         <v>20</v>
       </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1996,6 +2094,7 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2004,6 +2103,8 @@
       <c r="G35" t="n">
         <v>60</v>
       </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2027,6 +2128,7 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2035,6 +2137,8 @@
       <c r="G36" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2058,6 +2162,7 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2066,6 +2171,8 @@
       <c r="G37" t="n">
         <v>61.8</v>
       </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2089,6 +2196,7 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2097,6 +2205,8 @@
       <c r="G38" t="n">
         <v>54.384</v>
       </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2120,6 +2230,7 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2128,6 +2239,8 @@
       <c r="G39" t="n">
         <v>2630</v>
       </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2151,6 +2264,7 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2159,6 +2273,8 @@
       <c r="G40" t="n">
         <v>800</v>
       </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2182,6 +2298,7 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2190,6 +2307,8 @@
       <c r="G41" t="n">
         <v>274</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2213,6 +2332,7 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2221,6 +2341,8 @@
       <c r="G42" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2244,6 +2366,7 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2252,6 +2375,8 @@
       <c r="G43" t="n">
         <v>229.332</v>
       </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2275,6 +2400,7 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2283,6 +2409,8 @@
       <c r="G44" t="n">
         <v>7.004</v>
       </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2306,6 +2434,7 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2314,6 +2443,8 @@
       <c r="G45" t="n">
         <v>103</v>
       </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2337,6 +2468,7 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2345,6 +2477,8 @@
       <c r="G46" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2368,6 +2502,7 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2376,6 +2511,8 @@
       <c r="G47" t="n">
         <v>20</v>
       </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2399,6 +2536,7 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2407,6 +2545,8 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2430,6 +2570,7 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2438,6 +2579,8 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2461,6 +2604,7 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2469,6 +2613,8 @@
       <c r="G50" t="n">
         <v>60</v>
       </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2492,6 +2638,7 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2500,6 +2647,8 @@
       <c r="G51" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2523,6 +2672,7 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2531,6 +2681,8 @@
       <c r="G52" t="n">
         <v>61.8</v>
       </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2554,6 +2706,7 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2562,6 +2715,8 @@
       <c r="G53" t="n">
         <v>54.384</v>
       </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2585,6 +2740,7 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2593,6 +2749,8 @@
       <c r="G54" t="n">
         <v>113.0488</v>
       </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2616,6 +2774,7 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2624,6 +2783,8 @@
       <c r="G55" t="n">
         <v>1613.23</v>
       </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2647,6 +2808,7 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2655,6 +2817,8 @@
       <c r="G56" t="n">
         <v>645.48</v>
       </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2678,6 +2842,7 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2686,6 +2851,8 @@
       <c r="G57" t="n">
         <v>500.5</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2709,6 +2876,7 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2717,6 +2885,8 @@
       <c r="G58" t="n">
         <v>283.5</v>
       </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2740,6 +2910,7 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2748,6 +2919,8 @@
       <c r="G59" t="n">
         <v>250</v>
       </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2771,6 +2944,7 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2779,6 +2953,8 @@
       <c r="G60" t="n">
         <v>254.4787</v>
       </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2802,6 +2978,7 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2810,6 +2987,8 @@
       <c r="G61" t="n">
         <v>105.34</v>
       </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2833,6 +3012,7 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -2841,6 +3021,8 @@
       <c r="G62" t="n">
         <v>96.899</v>
       </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2864,6 +3046,7 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -2872,6 +3055,8 @@
       <c r="G63" t="n">
         <v>38.7596</v>
       </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2895,6 +3080,7 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2903,6 +3089,8 @@
       <c r="G64" t="n">
         <v>103</v>
       </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2926,6 +3114,7 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -2934,6 +3123,8 @@
       <c r="G65" t="n">
         <v>51.5</v>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2957,6 +3148,7 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -2965,6 +3157,8 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2988,6 +3182,7 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2996,6 +3191,8 @@
       <c r="G67" t="n">
         <v>61.8</v>
       </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3019,6 +3216,7 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3027,6 +3225,8 @@
       <c r="G68" t="n">
         <v>54.384</v>
       </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3050,6 +3250,7 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3058,6 +3259,8 @@
       <c r="G69" t="n">
         <v>50</v>
       </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3081,6 +3284,7 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3089,6 +3293,8 @@
       <c r="G70" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3112,6 +3318,7 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3120,6 +3327,8 @@
       <c r="G71" t="n">
         <v>50</v>
       </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3143,6 +3352,7 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3151,6 +3361,8 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3174,6 +3386,7 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3182,6 +3395,8 @@
       <c r="G73" t="n">
         <v>7.004</v>
       </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3205,6 +3420,7 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3213,6 +3429,8 @@
       <c r="G74" t="n">
         <v>34.3333</v>
       </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3236,6 +3454,7 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3244,6 +3463,8 @@
       <c r="G75" t="n">
         <v>27.4667</v>
       </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3267,6 +3488,7 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3275,6 +3497,8 @@
       <c r="G76" t="n">
         <v>36.9083</v>
       </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3298,6 +3522,7 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3306,6 +3531,8 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3329,6 +3556,7 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3337,6 +3565,8 @@
       <c r="G78" t="n">
         <v>60</v>
       </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3360,6 +3590,7 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3368,6 +3599,8 @@
       <c r="G79" t="n">
         <v>20</v>
       </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3391,6 +3624,7 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3399,6 +3633,8 @@
       <c r="G80" t="n">
         <v>60</v>
       </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3422,6 +3658,7 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3430,6 +3667,8 @@
       <c r="G81" t="n">
         <v>113.0488</v>
       </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3453,6 +3692,7 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3461,6 +3701,8 @@
       <c r="G82" t="n">
         <v>20</v>
       </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3484,6 +3726,7 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3492,6 +3735,8 @@
       <c r="G83" t="n">
         <v>20</v>
       </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3515,6 +3760,7 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3523,6 +3769,8 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3546,6 +3794,7 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3554,6 +3803,8 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3577,6 +3828,7 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3585,6 +3837,8 @@
       <c r="G86" t="n">
         <v>20</v>
       </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3608,6 +3862,7 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3616,6 +3871,8 @@
       <c r="G87" t="n">
         <v>20</v>
       </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3639,6 +3896,7 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3647,322 +3905,12 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
         </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>时点</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>本次变化</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>预期值</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>PDF值</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>差额</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段类型+非空检查通过</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>存量87条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在+类型检查通过</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="I4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-933.7074</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G5" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-669.3701</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="G6" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5198.0447</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4635</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-563.0447</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="n">
-        <v>4635</v>
-      </c>
-      <c r="G7" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5568.7074</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-820.6586</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="G8" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5681.7562</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4880.2539</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-801.5023</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -972,7 +973,6 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -981,8 +981,6 @@
       <c r="G2" t="n">
         <v>2630</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1006,7 +1004,6 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1015,8 +1012,6 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1040,7 +1035,6 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1049,8 +1043,6 @@
       <c r="G4" t="n">
         <v>274</v>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1074,7 +1066,6 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1083,8 +1074,6 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1108,7 +1097,6 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1117,8 +1105,6 @@
       <c r="G6" t="n">
         <v>229.332</v>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1142,7 +1128,6 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1151,8 +1136,6 @@
       <c r="G7" t="n">
         <v>2630</v>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1176,7 +1159,6 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1185,8 +1167,6 @@
       <c r="G8" t="n">
         <v>800</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1210,7 +1190,6 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1219,8 +1198,6 @@
       <c r="G9" t="n">
         <v>274</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1244,7 +1221,6 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1253,8 +1229,6 @@
       <c r="G10" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1278,7 +1252,6 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1287,8 +1260,6 @@
       <c r="G11" t="n">
         <v>229.332</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>本次股权转让后，公司股权结构如下：</t>
@@ -1312,7 +1283,6 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1321,8 +1291,6 @@
       <c r="G12" t="n">
         <v>2630</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1346,7 +1314,6 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1355,8 +1322,6 @@
       <c r="G13" t="n">
         <v>800</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1380,7 +1345,6 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1389,8 +1353,6 @@
       <c r="G14" t="n">
         <v>274</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1414,7 +1376,6 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1423,8 +1384,6 @@
       <c r="G15" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1448,7 +1407,6 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1457,8 +1415,6 @@
       <c r="G16" t="n">
         <v>229.332</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1482,7 +1438,6 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1491,8 +1446,6 @@
       <c r="G17" t="n">
         <v>7.004</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1516,7 +1469,6 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1525,8 +1477,6 @@
       <c r="G18" t="n">
         <v>103</v>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1550,7 +1500,6 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1559,8 +1508,6 @@
       <c r="G19" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1584,7 +1531,6 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1593,8 +1539,6 @@
       <c r="G20" t="n">
         <v>20</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1618,7 +1562,6 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1627,8 +1570,6 @@
       <c r="G21" t="n">
         <v>20</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1652,7 +1593,6 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1661,8 +1601,6 @@
       <c r="G22" t="n">
         <v>20</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1686,7 +1624,6 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1695,8 +1632,6 @@
       <c r="G23" t="n">
         <v>60</v>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
@@ -1720,7 +1655,6 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1729,8 +1663,6 @@
       <c r="G24" t="n">
         <v>2630</v>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1754,7 +1686,6 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1763,8 +1694,6 @@
       <c r="G25" t="n">
         <v>800</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1788,7 +1717,6 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1797,8 +1725,6 @@
       <c r="G26" t="n">
         <v>274</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1822,7 +1748,6 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1831,8 +1756,6 @@
       <c r="G27" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1856,7 +1779,6 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1865,8 +1787,6 @@
       <c r="G28" t="n">
         <v>229.332</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1890,7 +1810,6 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1899,8 +1818,6 @@
       <c r="G29" t="n">
         <v>7.004</v>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1924,7 +1841,6 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1933,8 +1849,6 @@
       <c r="G30" t="n">
         <v>103</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1958,7 +1872,6 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1967,8 +1880,6 @@
       <c r="G31" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -1992,7 +1903,6 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2001,8 +1911,6 @@
       <c r="G32" t="n">
         <v>20</v>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2026,7 +1934,6 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2035,8 +1942,6 @@
       <c r="G33" t="n">
         <v>20</v>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2060,7 +1965,6 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2069,8 +1973,6 @@
       <c r="G34" t="n">
         <v>20</v>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2094,7 +1996,6 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2103,8 +2004,6 @@
       <c r="G35" t="n">
         <v>60</v>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2128,7 +2027,6 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2137,8 +2035,6 @@
       <c r="G36" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2162,7 +2058,6 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2171,8 +2066,6 @@
       <c r="G37" t="n">
         <v>61.8</v>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2196,7 +2089,6 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2205,8 +2097,6 @@
       <c r="G38" t="n">
         <v>54.384</v>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
@@ -2230,7 +2120,6 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2239,8 +2128,6 @@
       <c r="G39" t="n">
         <v>2630</v>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2264,7 +2151,6 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2273,8 +2159,6 @@
       <c r="G40" t="n">
         <v>800</v>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2298,7 +2182,6 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2307,8 +2190,6 @@
       <c r="G41" t="n">
         <v>274</v>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2332,7 +2213,6 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2341,8 +2221,6 @@
       <c r="G42" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2366,7 +2244,6 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2375,8 +2252,6 @@
       <c r="G43" t="n">
         <v>229.332</v>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2400,7 +2275,6 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2409,8 +2283,6 @@
       <c r="G44" t="n">
         <v>7.004</v>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2434,7 +2306,6 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2443,8 +2314,6 @@
       <c r="G45" t="n">
         <v>103</v>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2468,7 +2337,6 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2477,8 +2345,6 @@
       <c r="G46" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2502,7 +2368,6 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2511,8 +2376,6 @@
       <c r="G47" t="n">
         <v>20</v>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2536,7 +2399,6 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2545,8 +2407,6 @@
       <c r="G48" t="n">
         <v>20</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2570,7 +2430,6 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2579,8 +2438,6 @@
       <c r="G49" t="n">
         <v>20</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2604,7 +2461,6 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2613,8 +2469,6 @@
       <c r="G50" t="n">
         <v>60</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2638,7 +2492,6 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2647,8 +2500,6 @@
       <c r="G51" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2672,7 +2523,6 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2681,8 +2531,6 @@
       <c r="G52" t="n">
         <v>61.8</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2706,7 +2554,6 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2715,8 +2562,6 @@
       <c r="G53" t="n">
         <v>54.384</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2740,7 +2585,6 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2749,8 +2593,6 @@
       <c r="G54" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
@@ -2774,7 +2616,6 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2783,8 +2624,6 @@
       <c r="G55" t="n">
         <v>1613.23</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2808,7 +2647,6 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2817,8 +2655,6 @@
       <c r="G56" t="n">
         <v>645.48</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2842,7 +2678,6 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2851,8 +2686,6 @@
       <c r="G57" t="n">
         <v>500.5</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2876,7 +2709,6 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2885,8 +2717,6 @@
       <c r="G58" t="n">
         <v>283.5</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2910,7 +2740,6 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2919,8 +2748,6 @@
       <c r="G59" t="n">
         <v>250</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2944,7 +2771,6 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2953,8 +2779,6 @@
       <c r="G60" t="n">
         <v>254.4787</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -2978,7 +2802,6 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2987,8 +2810,6 @@
       <c r="G61" t="n">
         <v>105.34</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3012,7 +2833,6 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -3021,8 +2841,6 @@
       <c r="G62" t="n">
         <v>96.899</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3046,7 +2864,6 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -3055,8 +2872,6 @@
       <c r="G63" t="n">
         <v>38.7596</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3080,7 +2895,6 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -3089,8 +2903,6 @@
       <c r="G64" t="n">
         <v>103</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3114,7 +2926,6 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -3123,8 +2934,6 @@
       <c r="G65" t="n">
         <v>51.5</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3148,7 +2957,6 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -3157,8 +2965,6 @@
       <c r="G66" t="n">
         <v>50</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3182,7 +2988,6 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -3191,8 +2996,6 @@
       <c r="G67" t="n">
         <v>61.8</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3216,7 +3019,6 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3225,8 +3027,6 @@
       <c r="G68" t="n">
         <v>54.384</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3250,7 +3050,6 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3259,8 +3058,6 @@
       <c r="G69" t="n">
         <v>50</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3284,7 +3081,6 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3293,8 +3089,6 @@
       <c r="G70" t="n">
         <v>66.66800000000001</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3318,7 +3112,6 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3327,8 +3120,6 @@
       <c r="G71" t="n">
         <v>50</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3352,7 +3143,6 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3361,8 +3151,6 @@
       <c r="G72" t="n">
         <v>50</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3386,7 +3174,6 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3395,8 +3182,6 @@
       <c r="G73" t="n">
         <v>7.004</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3420,7 +3205,6 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3429,8 +3213,6 @@
       <c r="G74" t="n">
         <v>34.3333</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3454,7 +3236,6 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3463,8 +3244,6 @@
       <c r="G75" t="n">
         <v>27.4667</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3488,7 +3267,6 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3497,8 +3275,6 @@
       <c r="G76" t="n">
         <v>36.9083</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3522,7 +3298,6 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3531,8 +3306,6 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3556,7 +3329,6 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3565,8 +3337,6 @@
       <c r="G78" t="n">
         <v>60</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3590,7 +3360,6 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3599,8 +3368,6 @@
       <c r="G79" t="n">
         <v>20</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3624,7 +3391,6 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3633,8 +3399,6 @@
       <c r="G80" t="n">
         <v>60</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3658,7 +3422,6 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3667,8 +3430,6 @@
       <c r="G81" t="n">
         <v>113.0488</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3692,7 +3453,6 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3701,8 +3461,6 @@
       <c r="G82" t="n">
         <v>20</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3726,7 +3484,6 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3735,8 +3492,6 @@
       <c r="G83" t="n">
         <v>20</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3760,7 +3515,6 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3769,8 +3523,6 @@
       <c r="G84" t="n">
         <v>20</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3794,7 +3546,6 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3803,8 +3554,6 @@
       <c r="G85" t="n">
         <v>20</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3828,7 +3577,6 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3837,8 +3585,6 @@
       <c r="G86" t="n">
         <v>20</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3862,7 +3608,6 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3871,8 +3616,6 @@
       <c r="G87" t="n">
         <v>20</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
@@ -3896,7 +3639,6 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
-      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3905,11 +3647,119 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>检查类型</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>时点</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>股东</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>校验结果</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>认缴15条</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>字段完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>存量87条</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>t0存在</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>schema</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>转让8条</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>已合并</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -3664,7 +3664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3675,20 +3675,45 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>时点</t>
+          <t>PDF页码</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>股东</t>
+          <t>股东/认购方</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>上一时点(万股)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>本次变化(万股)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>预期值(万股)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>PDF值(万股)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>差额(万股)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>校验结果</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -3703,17 +3728,22 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>认缴15条</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>认缴流量</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>字段完整</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15条,字段完整</t>
         </is>
       </c>
     </row>
@@ -3726,40 +3756,3002 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>存量87条</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>股权存量</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>t0存在</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>87条,t0存在</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>schema</t>
+          <t>cross_check_total</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>转让8条</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-933.7074</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4933.7074</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-669.3701</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4264.3373</v>
+      </c>
+      <c r="E6" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5198.0447</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4635</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-563.0447</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4635</v>
+      </c>
+      <c r="E7" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5568.7074</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-820.6586</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cross_check_total</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>总股本</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4748.0488</v>
+      </c>
+      <c r="E8" t="n">
+        <v>933.7074</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5681.7562</v>
+      </c>
+      <c r="G8" t="n">
+        <v>4880.2539</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-801.5023</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>丰利财富</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-66.66800000000001</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>274</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274</v>
+      </c>
+      <c r="G10" t="n">
+        <v>274</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>已合并</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>800</v>
+      </c>
+      <c r="E11" t="n">
+        <v>25</v>
+      </c>
+      <c r="F11" t="n">
+        <v>825</v>
+      </c>
+      <c r="G11" t="n">
+        <v>800</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G12" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>t0-&gt;t1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>274</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>274</v>
+      </c>
+      <c r="G15" t="n">
+        <v>274</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>800</v>
+      </c>
+      <c r="E16" t="n">
+        <v>25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>825</v>
+      </c>
+      <c r="G16" t="n">
+        <v>800</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G17" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>103</v>
+      </c>
+      <c r="F18" t="n">
+        <v>103</v>
+      </c>
+      <c r="G18" t="n">
+        <v>103</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F19" t="n">
+        <v>60</v>
+      </c>
+      <c r="G19" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="G20" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F25" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="G25" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F26" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>t1-&gt;t2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F28" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="G28" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>274</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>274</v>
+      </c>
+      <c r="G29" t="n">
+        <v>274</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>800</v>
+      </c>
+      <c r="E30" t="n">
+        <v>25</v>
+      </c>
+      <c r="F30" t="n">
+        <v>825</v>
+      </c>
+      <c r="G30" t="n">
+        <v>800</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G31" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>103</v>
+      </c>
+      <c r="E32" t="n">
+        <v>103</v>
+      </c>
+      <c r="F32" t="n">
+        <v>206</v>
+      </c>
+      <c r="G32" t="n">
+        <v>103</v>
+      </c>
+      <c r="H32" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>60</v>
+      </c>
+      <c r="E33" t="n">
+        <v>60</v>
+      </c>
+      <c r="F33" t="n">
+        <v>120</v>
+      </c>
+      <c r="G33" t="n">
+        <v>60</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F34" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="G34" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F35" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>20</v>
+      </c>
+      <c r="E38" t="n">
+        <v>20</v>
+      </c>
+      <c r="F38" t="n">
+        <v>40</v>
+      </c>
+      <c r="G38" t="n">
+        <v>20</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>20</v>
+      </c>
+      <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="n">
+        <v>40</v>
+      </c>
+      <c r="G39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="E40" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F40" t="n">
+        <v>68.6666</v>
+      </c>
+      <c r="G40" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-34.3333</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>20</v>
+      </c>
+      <c r="E41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" t="n">
+        <v>40</v>
+      </c>
+      <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>t2-&gt;t3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E42" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F42" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="G42" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="E43" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F43" t="n">
+        <v>108.768</v>
+      </c>
+      <c r="G43" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-54.384</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>274</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>274</v>
+      </c>
+      <c r="G44" t="n">
+        <v>274</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>800</v>
+      </c>
+      <c r="E45" t="n">
+        <v>25</v>
+      </c>
+      <c r="F45" t="n">
+        <v>825</v>
+      </c>
+      <c r="G45" t="n">
+        <v>800</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G46" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>103</v>
+      </c>
+      <c r="E47" t="n">
+        <v>103</v>
+      </c>
+      <c r="F47" t="n">
+        <v>206</v>
+      </c>
+      <c r="G47" t="n">
+        <v>103</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>60</v>
+      </c>
+      <c r="E48" t="n">
+        <v>60</v>
+      </c>
+      <c r="F48" t="n">
+        <v>120</v>
+      </c>
+      <c r="G48" t="n">
+        <v>60</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="E49" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F49" t="n">
+        <v>508.9574</v>
+      </c>
+      <c r="G49" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-254.4787</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E50" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F50" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G50" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G51" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G52" t="n">
+        <v>2630</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>20</v>
+      </c>
+      <c r="E53" t="n">
+        <v>20</v>
+      </c>
+      <c r="F53" t="n">
+        <v>40</v>
+      </c>
+      <c r="G53" t="n">
+        <v>20</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>20</v>
+      </c>
+      <c r="E54" t="n">
+        <v>20</v>
+      </c>
+      <c r="F54" t="n">
+        <v>40</v>
+      </c>
+      <c r="G54" t="n">
+        <v>20</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>火炬电子</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="F55" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="G55" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="E56" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="F56" t="n">
+        <v>68.6666</v>
+      </c>
+      <c r="G56" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-34.3333</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>20</v>
+      </c>
+      <c r="E57" t="n">
+        <v>20</v>
+      </c>
+      <c r="F57" t="n">
+        <v>40</v>
+      </c>
+      <c r="G57" t="n">
+        <v>20</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>t3-&gt;t4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="F58" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="G58" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-61.8</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>东方富海</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>250</v>
+      </c>
+      <c r="H59" t="n">
+        <v>250</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>中小企业基金</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>38.7596</v>
+      </c>
+      <c r="F60" t="n">
+        <v>38.7596</v>
+      </c>
+      <c r="G60" t="n">
+        <v>38.7596</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="E61" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="F61" t="n">
+        <v>108.768</v>
+      </c>
+      <c r="G61" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-54.384</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>临港投资</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" t="n">
+        <v>27.4667</v>
+      </c>
+      <c r="H62" t="n">
+        <v>27.4667</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>274</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>274</v>
+      </c>
+      <c r="G63" t="n">
+        <v>105.34</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-168.66</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>余满芬</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>20</v>
+      </c>
+      <c r="H64" t="n">
+        <v>20</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>800</v>
+      </c>
+      <c r="E65" t="n">
+        <v>25</v>
+      </c>
+      <c r="F65" t="n">
+        <v>825</v>
+      </c>
+      <c r="G65" t="n">
+        <v>645.48</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-179.52</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>229.332</v>
+      </c>
+      <c r="G66" t="n">
+        <v>500.5</v>
+      </c>
+      <c r="H66" t="n">
+        <v>271.168</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>103</v>
+      </c>
+      <c r="E67" t="n">
+        <v>103</v>
+      </c>
+      <c r="F67" t="n">
+        <v>206</v>
+      </c>
+      <c r="G67" t="n">
+        <v>103</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-103</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>厦门西堤</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="F68" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="G68" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>60</v>
+      </c>
+      <c r="E69" t="n">
+        <v>60</v>
+      </c>
+      <c r="F69" t="n">
+        <v>120</v>
+      </c>
+      <c r="G69" t="n">
+        <v>60</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-60</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="E70" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="F70" t="n">
+        <v>508.9574</v>
+      </c>
+      <c r="G70" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-254.4787</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="G71" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-7.004</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="G72" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>pass</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>富海深湾</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" t="n">
+        <v>50</v>
+      </c>
+      <c r="H73" t="n">
+        <v>50</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>富海节能</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H74" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>崔振南</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>20</v>
+      </c>
+      <c r="H75" t="n">
+        <v>20</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>昆山红土</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>50</v>
+      </c>
+      <c r="H76" t="n">
+        <v>50</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cross_check_shareholder</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2630</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2630</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1613.23</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-1016.77</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>t4-&gt;t5</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>5股东</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>t0比例合计71.02%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>5股东</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>t1比例合计72.69%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>12股东</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>t2比例合计109.13%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>15股东</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>t3比例合计117.12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>16股东</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>t4比例合计119.50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ratio_check</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>34股东</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>t5比例合计145.34%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_认缴流量" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_股权结构存量" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_schema_cross_check" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -973,6 +972,7 @@
       <c r="D2" t="n">
         <v>4000</v>
       </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -980,6 +980,10 @@
       </c>
       <c r="G2" t="n">
         <v>2630</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>35.02</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1004,6 +1008,7 @@
       <c r="D3" t="n">
         <v>4000</v>
       </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1011,6 +1016,12 @@
       </c>
       <c r="G3" t="n">
         <v>800</v>
+      </c>
+      <c r="H3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" t="n">
+        <v>18.86</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1035,6 +1046,7 @@
       <c r="D4" t="n">
         <v>4000</v>
       </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1042,6 +1054,10 @@
       </c>
       <c r="G4" t="n">
         <v>274</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>4.63</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1066,6 +1082,7 @@
       <c r="D5" t="n">
         <v>4000</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>丰利财富</t>
@@ -1074,6 +1091,8 @@
       <c r="G5" t="n">
         <v>66.66800000000001</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
@@ -1097,6 +1116,7 @@
       <c r="D6" t="n">
         <v>4000</v>
       </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1104,6 +1124,10 @@
       </c>
       <c r="G6" t="n">
         <v>229.332</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>12.51</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1128,6 +1152,7 @@
       <c r="D7" t="n">
         <v>4000</v>
       </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1135,6 +1160,10 @@
       </c>
       <c r="G7" t="n">
         <v>2630</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>35.02</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1159,6 +1188,7 @@
       <c r="D8" t="n">
         <v>4000</v>
       </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1166,6 +1196,12 @@
       </c>
       <c r="G8" t="n">
         <v>800</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25</v>
+      </c>
+      <c r="I8" t="n">
+        <v>18.86</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1190,6 +1226,7 @@
       <c r="D9" t="n">
         <v>4000</v>
       </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1197,6 +1234,10 @@
       </c>
       <c r="G9" t="n">
         <v>274</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>4.63</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1221,6 +1262,7 @@
       <c r="D10" t="n">
         <v>4000</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1228,6 +1270,10 @@
       </c>
       <c r="G10" t="n">
         <v>66.66800000000001</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>1.67</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1252,6 +1298,7 @@
       <c r="D11" t="n">
         <v>4000</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1259,6 +1306,10 @@
       </c>
       <c r="G11" t="n">
         <v>229.332</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>12.51</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1283,6 +1334,7 @@
       <c r="D12" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1290,6 +1342,10 @@
       </c>
       <c r="G12" t="n">
         <v>2630</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>35.02</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1314,6 +1370,7 @@
       <c r="D13" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1321,6 +1378,12 @@
       </c>
       <c r="G13" t="n">
         <v>800</v>
+      </c>
+      <c r="H13" t="n">
+        <v>25</v>
+      </c>
+      <c r="I13" t="n">
+        <v>18.86</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1345,6 +1408,7 @@
       <c r="D14" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1352,6 +1416,10 @@
       </c>
       <c r="G14" t="n">
         <v>274</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>4.63</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1376,6 +1444,7 @@
       <c r="D15" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1383,6 +1452,10 @@
       </c>
       <c r="G15" t="n">
         <v>66.66800000000001</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1.67</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1407,6 +1480,7 @@
       <c r="D16" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1414,6 +1488,10 @@
       </c>
       <c r="G16" t="n">
         <v>229.332</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>12.51</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1438,6 +1516,7 @@
       <c r="D17" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1445,6 +1524,10 @@
       </c>
       <c r="G17" t="n">
         <v>7.004</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>0.15</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1469,6 +1552,7 @@
       <c r="D18" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1476,6 +1560,10 @@
       </c>
       <c r="G18" t="n">
         <v>103</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="n">
+        <v>2.22</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1500,6 +1588,7 @@
       <c r="D19" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1507,6 +1596,10 @@
       </c>
       <c r="G19" t="n">
         <v>34.3333</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>0.74</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1531,6 +1624,7 @@
       <c r="D20" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1538,6 +1632,10 @@
       </c>
       <c r="G20" t="n">
         <v>20</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>9.43</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1562,6 +1660,7 @@
       <c r="D21" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1569,6 +1668,10 @@
       </c>
       <c r="G21" t="n">
         <v>20</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="n">
+        <v>0.43</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1593,6 +1696,7 @@
       <c r="D22" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1600,6 +1704,10 @@
       </c>
       <c r="G22" t="n">
         <v>20</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>3.07</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1624,6 +1732,7 @@
       <c r="D23" t="n">
         <v>4264.3373</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -1631,6 +1740,10 @@
       </c>
       <c r="G23" t="n">
         <v>60</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>20.4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1655,6 +1768,7 @@
       <c r="D24" t="n">
         <v>4635</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -1662,6 +1776,10 @@
       </c>
       <c r="G24" t="n">
         <v>2630</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>35.02</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1686,6 +1804,7 @@
       <c r="D25" t="n">
         <v>4635</v>
       </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -1693,6 +1812,12 @@
       </c>
       <c r="G25" t="n">
         <v>800</v>
+      </c>
+      <c r="H25" t="n">
+        <v>25</v>
+      </c>
+      <c r="I25" t="n">
+        <v>18.86</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1717,6 +1842,7 @@
       <c r="D26" t="n">
         <v>4635</v>
       </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -1724,6 +1850,10 @@
       </c>
       <c r="G26" t="n">
         <v>274</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>4.63</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1748,6 +1878,7 @@
       <c r="D27" t="n">
         <v>4635</v>
       </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -1755,6 +1886,10 @@
       </c>
       <c r="G27" t="n">
         <v>66.66800000000001</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>1.67</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1779,6 +1914,7 @@
       <c r="D28" t="n">
         <v>4635</v>
       </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -1786,6 +1922,10 @@
       </c>
       <c r="G28" t="n">
         <v>229.332</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="n">
+        <v>12.51</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1810,6 +1950,7 @@
       <c r="D29" t="n">
         <v>4635</v>
       </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -1817,6 +1958,10 @@
       </c>
       <c r="G29" t="n">
         <v>7.004</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="n">
+        <v>0.15</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1841,6 +1986,7 @@
       <c r="D30" t="n">
         <v>4635</v>
       </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -1848,6 +1994,10 @@
       </c>
       <c r="G30" t="n">
         <v>103</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>2.22</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1872,6 +2022,7 @@
       <c r="D31" t="n">
         <v>4635</v>
       </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -1879,6 +2030,10 @@
       </c>
       <c r="G31" t="n">
         <v>34.3333</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="n">
+        <v>0.74</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1903,6 +2058,7 @@
       <c r="D32" t="n">
         <v>4635</v>
       </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -1910,6 +2066,10 @@
       </c>
       <c r="G32" t="n">
         <v>20</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="n">
+        <v>9.43</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1934,6 +2094,7 @@
       <c r="D33" t="n">
         <v>4635</v>
       </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -1941,6 +2102,10 @@
       </c>
       <c r="G33" t="n">
         <v>20</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="n">
+        <v>0.43</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1965,6 +2130,7 @@
       <c r="D34" t="n">
         <v>4635</v>
       </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -1972,6 +2138,10 @@
       </c>
       <c r="G34" t="n">
         <v>20</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="n">
+        <v>3.07</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1996,6 +2166,7 @@
       <c r="D35" t="n">
         <v>4635</v>
       </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2003,6 +2174,10 @@
       </c>
       <c r="G35" t="n">
         <v>60</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>20.4</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -2027,6 +2202,7 @@
       <c r="D36" t="n">
         <v>4635</v>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2034,6 +2210,10 @@
       </c>
       <c r="G36" t="n">
         <v>254.4787</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>5.49</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -2058,6 +2238,7 @@
       <c r="D37" t="n">
         <v>4635</v>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2065,6 +2246,10 @@
       </c>
       <c r="G37" t="n">
         <v>61.8</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="n">
+        <v>1.33</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2089,6 +2274,7 @@
       <c r="D38" t="n">
         <v>4635</v>
       </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2096,6 +2282,10 @@
       </c>
       <c r="G38" t="n">
         <v>54.384</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="n">
+        <v>1.17</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2120,6 +2310,7 @@
       <c r="D39" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2127,6 +2318,10 @@
       </c>
       <c r="G39" t="n">
         <v>2630</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="n">
+        <v>35.02</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2151,6 +2346,7 @@
       <c r="D40" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2158,6 +2354,12 @@
       </c>
       <c r="G40" t="n">
         <v>800</v>
+      </c>
+      <c r="H40" t="n">
+        <v>25</v>
+      </c>
+      <c r="I40" t="n">
+        <v>18.86</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2182,6 +2384,7 @@
       <c r="D41" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2189,6 +2392,10 @@
       </c>
       <c r="G41" t="n">
         <v>274</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="n">
+        <v>4.63</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2213,6 +2420,7 @@
       <c r="D42" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -2220,6 +2428,10 @@
       </c>
       <c r="G42" t="n">
         <v>66.66800000000001</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="n">
+        <v>1.67</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2244,6 +2456,7 @@
       <c r="D43" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2251,6 +2464,10 @@
       </c>
       <c r="G43" t="n">
         <v>229.332</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="n">
+        <v>12.51</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2275,6 +2492,7 @@
       <c r="D44" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -2282,6 +2500,10 @@
       </c>
       <c r="G44" t="n">
         <v>7.004</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="n">
+        <v>0.15</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2306,6 +2528,7 @@
       <c r="D45" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2313,6 +2536,10 @@
       </c>
       <c r="G45" t="n">
         <v>103</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="n">
+        <v>2.22</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2337,6 +2564,7 @@
       <c r="D46" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -2344,6 +2572,10 @@
       </c>
       <c r="G46" t="n">
         <v>34.3333</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="n">
+        <v>0.74</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2368,6 +2600,7 @@
       <c r="D47" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -2375,6 +2608,10 @@
       </c>
       <c r="G47" t="n">
         <v>20</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="n">
+        <v>9.43</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2399,6 +2636,7 @@
       <c r="D48" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -2406,6 +2644,10 @@
       </c>
       <c r="G48" t="n">
         <v>20</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="n">
+        <v>0.43</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2430,6 +2672,7 @@
       <c r="D49" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -2437,6 +2680,10 @@
       </c>
       <c r="G49" t="n">
         <v>20</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="n">
+        <v>3.07</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2461,6 +2708,7 @@
       <c r="D50" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -2468,6 +2716,10 @@
       </c>
       <c r="G50" t="n">
         <v>60</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="n">
+        <v>20.4</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2492,6 +2744,7 @@
       <c r="D51" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2499,6 +2752,10 @@
       </c>
       <c r="G51" t="n">
         <v>254.4787</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="n">
+        <v>5.49</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2523,6 +2780,7 @@
       <c r="D52" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2530,6 +2788,10 @@
       </c>
       <c r="G52" t="n">
         <v>61.8</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="n">
+        <v>1.33</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2554,6 +2816,7 @@
       <c r="D53" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -2561,6 +2824,10 @@
       </c>
       <c r="G53" t="n">
         <v>54.384</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="n">
+        <v>1.17</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2585,6 +2852,7 @@
       <c r="D54" t="n">
         <v>4748.0488</v>
       </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -2592,6 +2860,10 @@
       </c>
       <c r="G54" t="n">
         <v>113.0488</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="n">
+        <v>2.38</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2616,6 +2888,7 @@
       <c r="D55" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
           <t>曾烨</t>
@@ -2623,6 +2896,10 @@
       </c>
       <c r="G55" t="n">
         <v>1613.23</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="n">
+        <v>35.02</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2647,6 +2924,7 @@
       <c r="D56" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
           <t>刘云锋</t>
@@ -2654,6 +2932,12 @@
       </c>
       <c r="G56" t="n">
         <v>645.48</v>
+      </c>
+      <c r="H56" t="n">
+        <v>25</v>
+      </c>
+      <c r="I56" t="n">
+        <v>18.86</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2678,6 +2962,7 @@
       <c r="D57" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
           <t>力源信息</t>
@@ -2685,6 +2970,10 @@
       </c>
       <c r="G57" t="n">
         <v>500.5</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="n">
+        <v>12.51</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2709,6 +2998,7 @@
       <c r="D58" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>芜湖富海</t>
@@ -2716,6 +3006,10 @@
       </c>
       <c r="G58" t="n">
         <v>283.5</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="n">
+        <v>7.09</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2740,6 +3034,7 @@
       <c r="D59" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
           <t>东方富海</t>
@@ -2747,6 +3042,10 @@
       </c>
       <c r="G59" t="n">
         <v>250</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="n">
+        <v>6.26</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2771,6 +3070,7 @@
       <c r="D60" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
           <t>国科瑞华</t>
@@ -2778,6 +3078,10 @@
       </c>
       <c r="G60" t="n">
         <v>254.4787</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>5.49</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2802,6 +3106,7 @@
       <c r="D61" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
           <t>为赛咨询</t>
@@ -2809,6 +3114,10 @@
       </c>
       <c r="G61" t="n">
         <v>105.34</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="n">
+        <v>4.63</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2833,6 +3142,7 @@
       <c r="D62" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
           <t>厦门西堤</t>
@@ -2840,6 +3150,10 @@
       </c>
       <c r="G62" t="n">
         <v>96.899</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="n">
+        <v>1.98</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2864,6 +3178,7 @@
       <c r="D63" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
           <t>中小企业基金</t>
@@ -2871,6 +3186,10 @@
       </c>
       <c r="G63" t="n">
         <v>38.7596</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="n">
+        <v>0.79</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2895,6 +3214,7 @@
       <c r="D64" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
           <t>南山富海</t>
@@ -2902,6 +3222,10 @@
       </c>
       <c r="G64" t="n">
         <v>103</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="n">
+        <v>2.22</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2926,6 +3250,7 @@
       <c r="D65" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
           <t>富海节能</t>
@@ -2933,6 +3258,10 @@
       </c>
       <c r="G65" t="n">
         <v>51.5</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="n">
+        <v>1.11</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -2957,6 +3286,7 @@
       <c r="D66" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
           <t>富海深湾</t>
@@ -2964,6 +3294,10 @@
       </c>
       <c r="G66" t="n">
         <v>50</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="n">
+        <v>0.83</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -2988,6 +3322,7 @@
       <c r="D67" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
           <t>CASREV FUND</t>
@@ -2995,6 +3330,10 @@
       </c>
       <c r="G67" t="n">
         <v>61.8</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="n">
+        <v>1.33</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3019,6 +3358,7 @@
       <c r="D68" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
           <t>中科贵银</t>
@@ -3026,6 +3366,10 @@
       </c>
       <c r="G68" t="n">
         <v>54.384</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="n">
+        <v>1.17</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3050,6 +3394,7 @@
       <c r="D69" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
           <t>深创投</t>
@@ -3057,6 +3402,10 @@
       </c>
       <c r="G69" t="n">
         <v>50</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="n">
+        <v>2.33</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3081,6 +3430,7 @@
       <c r="D70" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
           <t>天健创投</t>
@@ -3088,6 +3438,10 @@
       </c>
       <c r="G70" t="n">
         <v>66.66800000000001</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="n">
+        <v>1.67</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3112,6 +3466,7 @@
       <c r="D71" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
           <t>镇江红土</t>
@@ -3119,6 +3474,10 @@
       </c>
       <c r="G71" t="n">
         <v>50</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="n">
+        <v>0.83</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3143,6 +3502,7 @@
       <c r="D72" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
           <t>昆山红土</t>
@@ -3150,6 +3510,10 @@
       </c>
       <c r="G72" t="n">
         <v>50</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="n">
+        <v>0.83</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3174,6 +3538,7 @@
       <c r="D73" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
           <t>夏东</t>
@@ -3181,6 +3546,10 @@
       </c>
       <c r="G73" t="n">
         <v>7.004</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="n">
+        <v>0.15</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3205,6 +3574,7 @@
       <c r="D74" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
           <t>珠海拓域</t>
@@ -3212,6 +3582,10 @@
       </c>
       <c r="G74" t="n">
         <v>34.3333</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="n">
+        <v>0.74</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3236,6 +3610,7 @@
       <c r="D75" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
           <t>临港投资</t>
@@ -3243,6 +3618,10 @@
       </c>
       <c r="G75" t="n">
         <v>27.4667</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="n">
+        <v>0.59</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3267,6 +3646,7 @@
       <c r="D76" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
           <t>鸿迪投资</t>
@@ -3274,6 +3654,10 @@
       </c>
       <c r="G76" t="n">
         <v>36.9083</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="n">
+        <v>0.8</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3298,6 +3682,7 @@
       <c r="D77" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
           <t>李文发</t>
@@ -3305,6 +3690,10 @@
       </c>
       <c r="G77" t="n">
         <v>60</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
+        <v>9.43</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3329,6 +3718,7 @@
       <c r="D78" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
           <t>秦国君</t>
@@ -3336,6 +3726,10 @@
       </c>
       <c r="G78" t="n">
         <v>60</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>0.43</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3360,6 +3754,7 @@
       <c r="D79" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
           <t>李剑峰</t>
@@ -3367,6 +3762,10 @@
       </c>
       <c r="G79" t="n">
         <v>20</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="n">
+        <v>3.07</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3391,6 +3790,7 @@
       <c r="D80" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
           <t>周雪峰</t>
@@ -3398,6 +3798,10 @@
       </c>
       <c r="G80" t="n">
         <v>60</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>20.4</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3422,6 +3826,7 @@
       <c r="D81" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>火炬电子</t>
@@ -3429,6 +3834,10 @@
       </c>
       <c r="G81" t="n">
         <v>113.0488</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="n">
+        <v>2.38</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3453,6 +3862,7 @@
       <c r="D82" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
           <t>郦韩英</t>
@@ -3460,6 +3870,10 @@
       </c>
       <c r="G82" t="n">
         <v>20</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="n">
+        <v>0.99</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3484,6 +3898,7 @@
       <c r="D83" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
           <t>沈笑彦</t>
@@ -3491,6 +3906,10 @@
       </c>
       <c r="G83" t="n">
         <v>20</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="n">
+        <v>0.17</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3515,6 +3934,7 @@
       <c r="D84" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
           <t>衣嘉平</t>
@@ -3522,6 +3942,10 @@
       </c>
       <c r="G84" t="n">
         <v>20</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="n">
+        <v>0.17</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3546,6 +3970,7 @@
       <c r="D85" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
           <t>余满芬</t>
@@ -3553,6 +3978,10 @@
       </c>
       <c r="G85" t="n">
         <v>20</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="n">
+        <v>0.17</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3577,6 +4006,7 @@
       <c r="D86" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
           <t>崔振南</t>
@@ -3584,6 +4014,10 @@
       </c>
       <c r="G86" t="n">
         <v>20</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="n">
+        <v>0.08</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3608,6 +4042,7 @@
       <c r="D87" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
           <t>福建开京</t>
@@ -3615,6 +4050,10 @@
       </c>
       <c r="G87" t="n">
         <v>20</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="n">
+        <v>0.24</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3639,6 +4078,7 @@
       <c r="D88" t="n">
         <v>4883.7074</v>
       </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
           <t>湘裕君源</t>
@@ -3647,3111 +4087,13 @@
       <c r="G88" t="n">
         <v>15.9535</v>
       </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>0.58</v>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>本次变更完成后，发行人的股权结构如下：</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J83"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>检查类型</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>PDF页码</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>股东/认购方</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>上一时点(万股)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>本次变化(万股)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>预期值(万股)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>PDF值(万股)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>差额(万股)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>校验结果</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>认缴流量</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>15条,字段完整</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>schema</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>股权存量</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>87条,t0存在</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="G4" t="n">
-        <v>4000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-933.7074</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4933.7074</v>
-      </c>
-      <c r="G5" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-669.3701</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4264.3373</v>
-      </c>
-      <c r="E6" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5198.0447</v>
-      </c>
-      <c r="G6" t="n">
-        <v>4635</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-563.0447</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4635</v>
-      </c>
-      <c r="E7" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F7" t="n">
-        <v>5568.7074</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-820.6586</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cross_check_total</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>总股本</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4748.0488</v>
-      </c>
-      <c r="E8" t="n">
-        <v>933.7074</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5681.7562</v>
-      </c>
-      <c r="G8" t="n">
-        <v>4880.2539</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-801.5023</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>丰利财富</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-66.66800000000001</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>274</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>274</v>
-      </c>
-      <c r="G10" t="n">
-        <v>274</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>800</v>
-      </c>
-      <c r="E11" t="n">
-        <v>25</v>
-      </c>
-      <c r="F11" t="n">
-        <v>825</v>
-      </c>
-      <c r="G11" t="n">
-        <v>800</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G12" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>t0-&gt;t1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>274</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>274</v>
-      </c>
-      <c r="G15" t="n">
-        <v>274</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>800</v>
-      </c>
-      <c r="E16" t="n">
-        <v>25</v>
-      </c>
-      <c r="F16" t="n">
-        <v>825</v>
-      </c>
-      <c r="G16" t="n">
-        <v>800</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G17" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>103</v>
-      </c>
-      <c r="F18" t="n">
-        <v>103</v>
-      </c>
-      <c r="G18" t="n">
-        <v>103</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>60</v>
-      </c>
-      <c r="F19" t="n">
-        <v>60</v>
-      </c>
-      <c r="G19" t="n">
-        <v>60</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="G20" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G21" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23" t="n">
-        <v>20</v>
-      </c>
-      <c r="G23" t="n">
-        <v>20</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>20</v>
-      </c>
-      <c r="F24" t="n">
-        <v>20</v>
-      </c>
-      <c r="G24" t="n">
-        <v>20</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F25" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="G25" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>20</v>
-      </c>
-      <c r="F26" t="n">
-        <v>20</v>
-      </c>
-      <c r="G26" t="n">
-        <v>20</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>t1-&gt;t2</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F27" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="G27" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F28" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="G28" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>274</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>274</v>
-      </c>
-      <c r="G29" t="n">
-        <v>274</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>800</v>
-      </c>
-      <c r="E30" t="n">
-        <v>25</v>
-      </c>
-      <c r="F30" t="n">
-        <v>825</v>
-      </c>
-      <c r="G30" t="n">
-        <v>800</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G31" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>103</v>
-      </c>
-      <c r="E32" t="n">
-        <v>103</v>
-      </c>
-      <c r="F32" t="n">
-        <v>206</v>
-      </c>
-      <c r="G32" t="n">
-        <v>103</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>60</v>
-      </c>
-      <c r="E33" t="n">
-        <v>60</v>
-      </c>
-      <c r="F33" t="n">
-        <v>120</v>
-      </c>
-      <c r="G33" t="n">
-        <v>60</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F34" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="G34" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E35" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F35" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G35" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G36" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>20</v>
-      </c>
-      <c r="E38" t="n">
-        <v>20</v>
-      </c>
-      <c r="F38" t="n">
-        <v>40</v>
-      </c>
-      <c r="G38" t="n">
-        <v>20</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>20</v>
-      </c>
-      <c r="E39" t="n">
-        <v>20</v>
-      </c>
-      <c r="F39" t="n">
-        <v>40</v>
-      </c>
-      <c r="G39" t="n">
-        <v>20</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="E40" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F40" t="n">
-        <v>68.6666</v>
-      </c>
-      <c r="G40" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-34.3333</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>20</v>
-      </c>
-      <c r="E41" t="n">
-        <v>20</v>
-      </c>
-      <c r="F41" t="n">
-        <v>40</v>
-      </c>
-      <c r="G41" t="n">
-        <v>20</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>t2-&gt;t3</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="E42" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F42" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="G42" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-61.8</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="E43" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F43" t="n">
-        <v>108.768</v>
-      </c>
-      <c r="G43" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-54.384</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>274</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>274</v>
-      </c>
-      <c r="G44" t="n">
-        <v>274</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>800</v>
-      </c>
-      <c r="E45" t="n">
-        <v>25</v>
-      </c>
-      <c r="F45" t="n">
-        <v>825</v>
-      </c>
-      <c r="G45" t="n">
-        <v>800</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G46" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>103</v>
-      </c>
-      <c r="E47" t="n">
-        <v>103</v>
-      </c>
-      <c r="F47" t="n">
-        <v>206</v>
-      </c>
-      <c r="G47" t="n">
-        <v>103</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>60</v>
-      </c>
-      <c r="E48" t="n">
-        <v>60</v>
-      </c>
-      <c r="F48" t="n">
-        <v>120</v>
-      </c>
-      <c r="G48" t="n">
-        <v>60</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="E49" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F49" t="n">
-        <v>508.9574</v>
-      </c>
-      <c r="G49" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-254.4787</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E50" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F50" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G50" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G51" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G52" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>李剑峰</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>20</v>
-      </c>
-      <c r="E53" t="n">
-        <v>20</v>
-      </c>
-      <c r="F53" t="n">
-        <v>40</v>
-      </c>
-      <c r="G53" t="n">
-        <v>20</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>李文发</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>20</v>
-      </c>
-      <c r="E54" t="n">
-        <v>20</v>
-      </c>
-      <c r="F54" t="n">
-        <v>40</v>
-      </c>
-      <c r="G54" t="n">
-        <v>20</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>火炬电子</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="F55" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="G55" t="n">
-        <v>113.0488</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>珠海拓域</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="E56" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="F56" t="n">
-        <v>68.6666</v>
-      </c>
-      <c r="G56" t="n">
-        <v>34.3333</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-34.3333</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>秦国君</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>20</v>
-      </c>
-      <c r="E57" t="n">
-        <v>20</v>
-      </c>
-      <c r="F57" t="n">
-        <v>40</v>
-      </c>
-      <c r="G57" t="n">
-        <v>20</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-20</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>t3-&gt;t4</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CASREV FUND</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="E58" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="F58" t="n">
-        <v>123.6</v>
-      </c>
-      <c r="G58" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-61.8</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>东方富海</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>250</v>
-      </c>
-      <c r="H59" t="n">
-        <v>250</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>中小企业基金</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>38.7596</v>
-      </c>
-      <c r="F60" t="n">
-        <v>38.7596</v>
-      </c>
-      <c r="G60" t="n">
-        <v>38.7596</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>中科贵银</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="E61" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="F61" t="n">
-        <v>108.768</v>
-      </c>
-      <c r="G61" t="n">
-        <v>54.384</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-54.384</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>临港投资</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>27.4667</v>
-      </c>
-      <c r="H62" t="n">
-        <v>27.4667</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>274</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="n">
-        <v>274</v>
-      </c>
-      <c r="G63" t="n">
-        <v>105.34</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-168.66</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>余满芬</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>20</v>
-      </c>
-      <c r="H64" t="n">
-        <v>20</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>刘云锋</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>800</v>
-      </c>
-      <c r="E65" t="n">
-        <v>25</v>
-      </c>
-      <c r="F65" t="n">
-        <v>825</v>
-      </c>
-      <c r="G65" t="n">
-        <v>645.48</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-179.52</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>力源信息</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="n">
-        <v>229.332</v>
-      </c>
-      <c r="G66" t="n">
-        <v>500.5</v>
-      </c>
-      <c r="H66" t="n">
-        <v>271.168</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>南山富海</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>103</v>
-      </c>
-      <c r="E67" t="n">
-        <v>103</v>
-      </c>
-      <c r="F67" t="n">
-        <v>206</v>
-      </c>
-      <c r="G67" t="n">
-        <v>103</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-103</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>厦门西堤</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="F68" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="G68" t="n">
-        <v>96.899</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>周雪峰</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>60</v>
-      </c>
-      <c r="E69" t="n">
-        <v>60</v>
-      </c>
-      <c r="F69" t="n">
-        <v>120</v>
-      </c>
-      <c r="G69" t="n">
-        <v>60</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-60</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>国科瑞华</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="E70" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="F70" t="n">
-        <v>508.9574</v>
-      </c>
-      <c r="G70" t="n">
-        <v>254.4787</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-254.4787</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>夏东</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E71" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="F71" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G71" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-7.004</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>天健创投</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="G72" t="n">
-        <v>66.66800000000001</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>pass</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>富海深湾</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" t="n">
-        <v>50</v>
-      </c>
-      <c r="H73" t="n">
-        <v>50</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>富海节能</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H74" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>崔振南</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" t="n">
-        <v>20</v>
-      </c>
-      <c r="H75" t="n">
-        <v>20</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>昆山红土</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
-      <c r="G76" t="n">
-        <v>50</v>
-      </c>
-      <c r="H76" t="n">
-        <v>50</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>cross_check_shareholder</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>2630</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="n">
-        <v>2630</v>
-      </c>
-      <c r="G77" t="n">
-        <v>1613.23</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-1016.77</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>t4-&gt;t5</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>5股东</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>t0比例合计71.02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>5股东</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>t1比例合计72.69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>12股东</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>t2比例合计109.13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>15股东</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>t3比例合计117.12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>16股东</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>t4比例合计119.50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>ratio_check</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>34股东</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>待复核</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>t5比例合计145.34%</t>
         </is>
       </c>
     </row>

--- a/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
+++ b/outputs/week2_excel/301563_云汉芯城_三表抽取.xlsx
@@ -900,7 +900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -957,1829 +957,1713 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2015年12月3日整体变更设立时股权结构</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>曾烨</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>2630</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>深圳市云汉电子有限公司</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>25</v>
+      </c>
       <c r="I2" t="n">
-        <v>35.02</v>
+        <v>50</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2015年12月3日整体变更设立时股权结构</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>刘云锋</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>800</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>25</v>
       </c>
       <c r="I3" t="n">
-        <v>18.86</v>
+        <v>50</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2015年12月3日整体变更设立时股权结构</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>为赛咨询</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>274</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="n">
-        <v>4.63</v>
-      </c>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>100</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2015年12月3日整体变更设立时股权结构</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>丰利财富</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>66.66800000000001</v>
+        <v>1779.2</v>
       </c>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="n">
+        <v>44.48</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t0</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2015年12月3日整体变更设立时股权结构</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>力源信息</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>229.332</v>
+        <v>741.336</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>12.51</v>
+        <v>18.53</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>本公司整体变更设立时，发起人持有本公司的股份数量及比例如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2018年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>力源信息</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2630</v>
+        <v>500.4</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>35.02</v>
+        <v>12.51</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>本次股权转让后，公司股权结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2018年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>芜湖富海</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>800</v>
-      </c>
-      <c r="H8" t="n">
-        <v>25</v>
-      </c>
+        <v>283.532</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>18.86</v>
+        <v>7.09</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>本次股权转让后，公司股权结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2018年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>为赛咨询</t>
+          <t>东方富海</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>274</v>
+        <v>250.2</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>4.63</v>
+        <v>6.26</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>本次股权转让后，公司股权结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2018年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>天健创投</t>
+          <t>为赛咨询</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>66.66800000000001</v>
+        <v>185.336</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>1.67</v>
+        <v>4.63</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>本次股权转让后，公司股权结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t1</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2018年4月第一次股权转让后股权结构</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>4000</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>力源信息</t>
+          <t>深创投</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>229.332</v>
+        <v>93.33199999999999</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>12.51</v>
+        <v>2.33</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>本次股权转让后，公司股权结构如下：</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>天健创投</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2630</v>
+        <v>66.66800000000001</v>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>35.02</v>
+        <v>1.67</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>镇江红土</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>800</v>
-      </c>
-      <c r="H13" t="n">
-        <v>25</v>
-      </c>
+        <v>33.332</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>18.86</v>
+        <v>0.83</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>为赛咨询</t>
+          <t>昆山红土</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>274</v>
+        <v>33.332</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>4.63</v>
+        <v>0.83</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>天健创投</t>
+          <t>富海深湾</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>66.66800000000001</v>
+        <v>33.332</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>1.67</v>
+        <v>0.83</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>力源信息</t>
+          <t>40,000,000</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>229.332</v>
+        <v>100</v>
       </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="n">
-        <v>12.51</v>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>7.004</v>
+        <v>1709.675</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>0.15</v>
+        <v>36.89</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>南山富海</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>103</v>
+        <v>694.986</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>2.22</v>
+        <v>14.99</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>珠海拓域</t>
+          <t>力源信息</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>34.3333</v>
+        <v>500.4</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>0.74</v>
+        <v>10.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>李文发</t>
+          <t>芜湖富海</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>283.532</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>9.43</v>
+        <v>6.12</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>秦国君</t>
+          <t>国科瑞华</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>254.4787</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.43</v>
+        <v>5.49</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>李剑峰</t>
+          <t>东方富海</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>250.2</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>3.07</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t2</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2018年6月第一次增资后股权结构（2018年6月28日）</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>4264.3373</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>周雪峰</t>
+          <t>为赛咨询</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>60</v>
+        <v>185.336</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>20.4</v>
+        <v>4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,000万元增至4,264.3373万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>南山富海</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2630</v>
+        <v>103</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>35.02</v>
+        <v>2.22</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>深创投</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>800</v>
-      </c>
-      <c r="H25" t="n">
-        <v>25</v>
-      </c>
+        <v>93.33199999999999</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>18.86</v>
+        <v>2.01</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>为赛咨询</t>
+          <t>天健创投</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>274</v>
+        <v>66.66800000000001</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="n">
-        <v>4.63</v>
+        <v>1.44</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>天健创投</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>66.66800000000001</v>
+        <v>61.8</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>力源信息</t>
+          <t>周雪峰</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>229.332</v>
+        <v>60</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="n">
-        <v>12.51</v>
+        <v>1.29</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>中科贵银</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>7.004</v>
+        <v>54.384</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
-        <v>0.15</v>
+        <v>1.17</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>南山富海</t>
+          <t>富海节能</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>103</v>
+        <v>51.5</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="n">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>珠海拓域</t>
+          <t>鸿迪投资</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>34.3333</v>
+        <v>36.9083</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>李文发</t>
+          <t>珠海拓域</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>34.3333</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="n">
-        <v>9.43</v>
+        <v>0.74</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>秦国君</t>
+          <t>富海深湾</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>33.332</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="n">
-        <v>0.43</v>
+        <v>0.72</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>李剑峰</t>
+          <t>镇江红土</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>33.332</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>3.07</v>
+        <v>0.72</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>周雪峰</t>
+          <t>昆山红土</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>33.332</v>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="n">
-        <v>20.4</v>
+        <v>0.72</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>国科瑞华</t>
+          <t>临港投资</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>254.4787</v>
+        <v>27.4667</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="n">
-        <v>5.49</v>
+        <v>0.59</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>李文发</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>61.8</v>
+        <v>20</v>
       </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="n">
-        <v>1.33</v>
+        <v>0.43</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>t3</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2018年7月第二次增资后股权结构（2018年7月27日）</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>4635</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>中科贵银</t>
+          <t>李剑峰</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>54.384</v>
+        <v>20</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="n">
-        <v>1.17</v>
+        <v>0.43</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,264.3373万元增至4,635万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>秦国君</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>2630</v>
+        <v>20</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="n">
-        <v>35.02</v>
+        <v>0.43</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>800</v>
-      </c>
-      <c r="H40" t="n">
-        <v>25</v>
-      </c>
+        <v>7.004</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
-        <v>18.86</v>
+        <v>0.15</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>设立时 | 股份公司设立</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>设立时 | 股份公司设立</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>为赛咨询</t>
+          <t>46,350,000</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>274</v>
+        <v>100</v>
       </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="n">
-        <v>4.63</v>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: 设立时 | 股份公司设立, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>天健创投</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>66.66800000000001</v>
+        <v>1709.675</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="n">
-        <v>1.67</v>
+        <v>36.89</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>力源信息</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>229.332</v>
+        <v>694.986</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
-        <v>12.51</v>
+        <v>14.99</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>力源信息</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>7.004</v>
+        <v>500.4</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="n">
-        <v>0.15</v>
+        <v>10.8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>南山富海</t>
+          <t>芜湖富海</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>103</v>
+        <v>283.532</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="n">
-        <v>2.22</v>
+        <v>6.12</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>珠海拓域</t>
+          <t>国科瑞华</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>34.3333</v>
+        <v>254.4787</v>
       </c>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="n">
-        <v>0.74</v>
+        <v>5.49</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>李文发</t>
+          <t>东方富海</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>20</v>
+        <v>250.2</v>
       </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="n">
-        <v>9.43</v>
+        <v>5.4</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>秦国君</t>
+          <t>为赛咨询</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>20</v>
+        <v>105.336</v>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0.43</v>
+        <v>2.27</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>李剑峰</t>
+          <t>南山富海</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>20</v>
+        <v>103</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>3.07</v>
+        <v>2.22</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>周雪峰</t>
+          <t>深创投</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>60</v>
+        <v>93.33199999999999</v>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="n">
-        <v>20.4</v>
+        <v>2.01</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>国科瑞华</t>
+          <t>天健创投</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>254.4787</v>
+        <v>66.66800000000001</v>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
-        <v>5.49</v>
+        <v>1.44</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
@@ -2795,1005 +2679,945 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>中科贵银</t>
+          <t>周雪峰</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>54.384</v>
+        <v>60</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>t4</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2020年5月第三次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>4748.0488</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>火炬电子</t>
+          <t>李文发</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>113.0488</v>
+        <v>60</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="n">
-        <v>2.38</v>
+        <v>1.29</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>发行人的注册资本由4,635万元增至4,748.0488万元。</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>曾烨</t>
+          <t>秦国君</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1613.23</v>
+        <v>60</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="n">
-        <v>35.02</v>
+        <v>1.29</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>刘云锋</t>
+          <t>中科贵银</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>645.48</v>
-      </c>
-      <c r="H56" t="n">
-        <v>25</v>
-      </c>
+        <v>54.384</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="n">
-        <v>18.86</v>
+        <v>1.17</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>力源信息</t>
+          <t>富海节能</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>500.5</v>
+        <v>51.5</v>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="n">
-        <v>12.51</v>
+        <v>1.11</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>芜湖富海</t>
+          <t>鸿迪投资</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>283.5</v>
+        <v>36.9083</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="n">
-        <v>7.09</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>东方富海</t>
+          <t>珠海拓域</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>250</v>
+        <v>34.3333</v>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
-        <v>6.26</v>
+        <v>0.74</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>国科瑞华</t>
+          <t>镇江红土</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>254.4787</v>
+        <v>33.332</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="n">
-        <v>5.49</v>
+        <v>0.72</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>为赛咨询</t>
+          <t>昆山红土</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>105.34</v>
+        <v>33.332</v>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="n">
-        <v>4.63</v>
+        <v>0.72</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>厦门西堤</t>
+          <t>富海深湾</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>96.899</v>
+        <v>33.332</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
-        <v>1.98</v>
+        <v>0.72</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>中小企业基金</t>
+          <t>临港投资</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>38.7596</v>
+        <v>27.4667</v>
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="n">
-        <v>0.79</v>
+        <v>0.59</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>南山富海</t>
+          <t>李剑峰</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="n">
-        <v>2.22</v>
+        <v>0.43</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>富海节能</t>
+          <t>夏东</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>51.5</v>
+        <v>7.004</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="n">
-        <v>1.11</v>
+        <v>0.15</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>（二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>富海深湾</t>
+          <t>46,350,000</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="n">
-        <v>0.83</v>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: （二）2018年 6月至 7月，股份公司增加注册资本暨第二次股权转让 | （三）2019年 8月，股份公司第三次股权转让, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CASREV FUND</t>
+          <t>曾烨</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>61.8</v>
+        <v>1709.675</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="n">
-        <v>1.33</v>
+        <v>36.01</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>中科贵银</t>
+          <t>刘云锋</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>54.384</v>
+        <v>694.986</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="n">
-        <v>1.17</v>
+        <v>14.64</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>深创投</t>
+          <t>力源信息</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>50</v>
+        <v>500.4</v>
       </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="n">
-        <v>2.33</v>
+        <v>10.54</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>天健创投</t>
+          <t>芜湖富海</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>66.66800000000001</v>
+        <v>283.532</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="n">
-        <v>1.67</v>
+        <v>5.97</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>镇江红土</t>
+          <t>国科瑞华</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>50</v>
+        <v>254.4787</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>0.83</v>
+        <v>5.36</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>昆山红土</t>
+          <t>东方富海</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>50</v>
+        <v>250.2</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>0.83</v>
+        <v>5.27</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>夏东</t>
+          <t>火炬电子</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>7.004</v>
+        <v>113.0488</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="n">
-        <v>0.15</v>
+        <v>2.38</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>珠海拓域</t>
+          <t>为赛咨询</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>34.3333</v>
+        <v>105.336</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="n">
-        <v>0.74</v>
+        <v>2.22</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>临港投资</t>
+          <t>南山富海</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>27.4667</v>
+        <v>103</v>
       </c>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="n">
-        <v>0.59</v>
+        <v>2.17</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>鸿迪投资</t>
+          <t>深创投</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>36.9083</v>
+        <v>93.33199999999999</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>1.97</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>李文发</t>
+          <t>天健创投</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>60</v>
+        <v>66.66800000000001</v>
       </c>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="n">
-        <v>9.43</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>秦国君</t>
+          <t>CASREV FUND</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="n">
-        <v>0.43</v>
+        <v>1.3</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>李剑峰</t>
+          <t>周雪峰</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
-        <v>3.07</v>
+        <v>1.26</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>周雪峰</t>
+          <t>李文发</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -3801,299 +3625,1605 @@
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="n">
-        <v>20.4</v>
+        <v>1.26</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>火炬电子</t>
+          <t>秦国君</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>113.0488</v>
+        <v>60</v>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="n">
-        <v>2.38</v>
+        <v>1.26</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>郦韩英</t>
+          <t>中科贵银</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>20</v>
+        <v>54.384</v>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="n">
-        <v>0.99</v>
+        <v>1.15</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>沈笑彦</t>
+          <t>富海节能</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>20</v>
+        <v>51.5</v>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="n">
-        <v>0.17</v>
+        <v>1.08</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>衣嘉平</t>
+          <t>鸿迪投资</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>20</v>
+        <v>36.9083</v>
       </c>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="n">
-        <v>0.17</v>
+        <v>0.78</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>余满芬</t>
+          <t>珠海拓域</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>20</v>
+        <v>34.3333</v>
       </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="n">
-        <v>0.17</v>
+        <v>0.72</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>崔振南</t>
+          <t>镇江红土</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>20</v>
+        <v>33.332</v>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="n">
-        <v>0.08</v>
+        <v>0.7</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>福建开京</t>
+          <t>昆山红土</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>20</v>
+        <v>33.332</v>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="n">
-        <v>0.24</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>t5</t>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2020年9月第四次增资后股权结构</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>4883.7074</v>
-      </c>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>湘裕君源</t>
+          <t>富海深湾</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>15.9535</v>
+        <v>33.332</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>0</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>临港投资</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>27.4667</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="n">
         <v>0.58</v>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>本次变更完成后，发行人的股权结构如下：</t>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>0</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>20</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>0</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>0</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>47,480,488</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>100</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>0</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>曾烨</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1613.2255</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>0</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>刘云锋</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>645.482</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>0</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>500.4</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>0</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>芜湖富海</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>283.532</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>0</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>国科瑞华</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>254.4787</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>0</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>东方富海</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>250.2</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>0</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>火炬电子</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>113.0488</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>0</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>为赛咨询</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>105.336</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>0</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>南山富海</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>103</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>0</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>厦门西堤</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>0</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>深创投</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>93.33199999999999</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>0</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>鸿迪投资</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>84.9083</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>0</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>天健创投</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>66.66800000000001</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>0</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>CASREV FUND</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>0</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>周雪峰</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>60</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>0</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>李文发</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>55</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>0</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>中科贵银</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>54.384</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>0</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>富海节能</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>0</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>郦韩英</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>48.4495</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>0</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>秦国君</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>45</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>0</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>中小企业基金</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>38.7596</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>0</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>珠海拓域</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>34.3333</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>0</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>富海深湾</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>33.332</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>0</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>镇江红土</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>33.332</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>0</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>昆山红土</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>33.332</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>0</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>湘裕君源</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>0</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>临港投资</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>27.4667</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>0</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>李剑峰</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>20</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>0</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>福建开京</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>11.628</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>沈笑彦</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>0</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>衣嘉平</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>0</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>余满芬</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>0</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>夏东</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>0</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>崔振南</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>38760</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>0</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>增资后，发行人的股权结构 | 本次增资后</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>48,837,074</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>100</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Markdown表格: 增资后，发行人的股权结构 | 本次增资后, 比例合计100.0%</t>
         </is>
       </c>
     </row>
